--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -175,15 +175,81 @@
     <t>&gt;=7</t>
   </si>
   <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ New York Mets</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>AJ Smith-Shawver</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>JT Ginn</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
     <t>Joey Cantillo</t>
   </si>
   <si>
     <t>Cleveland Guardians @ Los Angeles Angels</t>
   </si>
   <si>
-    <t>6-7</t>
-  </si>
-  <si>
     <t>Grayson Rodriguez</t>
   </si>
   <si>
@@ -193,25 +259,7 @@
     <t>Pittsburgh Pirates @ San Diego Padres</t>
   </si>
   <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
+    <t>Randy Vásquez</t>
   </si>
   <si>
     <t>Tanner Gordon</t>
@@ -235,43 +283,10 @@
     <t>Kansas City Royals @ Toronto Blue Jays</t>
   </si>
   <si>
-    <t>Dustin May</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ New York Mets</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
+    <t>Spencer Miles</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>J.T. Ginn</t>
@@ -655,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM27"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -787,6 +802,15 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+      <c r="D2">
+        <v>-113</v>
+      </c>
+      <c r="E2">
+        <v>-111</v>
+      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
@@ -806,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>0.2146</v>
@@ -879,6 +903,15 @@
       <c r="B3" t="s">
         <v>46</v>
       </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+      <c r="D3">
+        <v>-165</v>
+      </c>
+      <c r="E3">
+        <v>132</v>
+      </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
@@ -898,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>0.2141</v>
@@ -971,6 +1004,15 @@
       <c r="B4" t="s">
         <v>47</v>
       </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+      <c r="D4">
+        <v>-113</v>
+      </c>
+      <c r="E4">
+        <v>-102</v>
+      </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
@@ -990,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>0.1864</v>
@@ -1063,6 +1105,15 @@
       <c r="B5" t="s">
         <v>49</v>
       </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>132</v>
+      </c>
+      <c r="E5">
+        <v>-143</v>
+      </c>
       <c r="F5" t="s">
         <v>48</v>
       </c>
@@ -1082,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>0.1732</v>
@@ -1155,6 +1206,15 @@
       <c r="B6" t="s">
         <v>50</v>
       </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+      <c r="D6">
+        <v>-125</v>
+      </c>
+      <c r="E6">
+        <v>-101</v>
+      </c>
       <c r="F6" t="s">
         <v>51</v>
       </c>
@@ -1174,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>0.1746</v>
@@ -1247,6 +1307,15 @@
       <c r="B7" t="s">
         <v>52</v>
       </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+      <c r="D7">
+        <v>-128</v>
+      </c>
+      <c r="E7">
+        <v>104</v>
+      </c>
       <c r="F7" t="s">
         <v>51</v>
       </c>
@@ -1266,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7">
         <v>0.2265</v>
@@ -1339,17 +1408,26 @@
       <c r="B8" t="s">
         <v>54</v>
       </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+      <c r="D8">
+        <v>126</v>
+      </c>
+      <c r="E8">
+        <v>-162</v>
+      </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>823988</v>
+        <v>823096</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1358,46 +1436,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>0.2553</v>
+        <v>0.2433</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="P8">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="Q8">
-        <v>0.3146</v>
+        <v>0.2478</v>
       </c>
       <c r="R8">
-        <v>0.308</v>
+        <v>0.361</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2482</v>
+        <v>0.1536</v>
       </c>
       <c r="U8">
-        <v>0.2411</v>
+        <v>0.1554</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2528</v>
+        <v>0.2212</v>
       </c>
       <c r="X8">
         <v>0.2227</v>
       </c>
       <c r="Y8">
-        <v>1.0373</v>
+        <v>0.9613</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1406,22 +1484,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>6.61</v>
+        <v>3.81</v>
       </c>
       <c r="AE8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2736</v>
+        <v>0.2449</v>
       </c>
       <c r="AG8">
-        <v>1.1146</v>
+        <v>0.6899</v>
       </c>
       <c r="AH8">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM8">
-        <v>6.4</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1429,19 +1507,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>6.5</v>
+      </c>
+      <c r="D9">
+        <v>-162</v>
+      </c>
+      <c r="E9">
+        <v>126</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
       <c r="G9">
-        <v>823988</v>
+        <v>823096</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1450,46 +1537,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>0.2047</v>
+        <v>0.3008</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="P9">
-        <v>4.52</v>
+        <v>4.13</v>
       </c>
       <c r="Q9">
-        <v>0.2768</v>
+        <v>0.3088</v>
       </c>
       <c r="R9">
-        <v>0.359</v>
+        <v>0.405</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2046</v>
+        <v>0.2343</v>
       </c>
       <c r="U9">
-        <v>0.1828</v>
+        <v>0.216</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2107</v>
+        <v>0.2428</v>
       </c>
       <c r="X9">
         <v>0.2227</v>
       </c>
       <c r="Y9">
-        <v>0.9381</v>
+        <v>0.9826</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1498,22 +1585,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.23</v>
+        <v>7.8</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF9">
-        <v>0.2306</v>
+        <v>0.304</v>
       </c>
       <c r="AG9">
-        <v>0.9186</v>
+        <v>1.052</v>
       </c>
       <c r="AH9">
-        <v>0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="AM9">
-        <v>4.43</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1521,19 +1608,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10">
+        <v>3.5</v>
+      </c>
+      <c r="D10">
+        <v>-128</v>
+      </c>
+      <c r="E10">
+        <v>107</v>
+      </c>
+      <c r="F10" t="s">
         <v>58</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10">
+        <v>823825</v>
+      </c>
+      <c r="H10" t="s">
         <v>59</v>
       </c>
-      <c r="G10">
-        <v>823255</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1542,46 +1638,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>0.2084</v>
+        <v>0.2</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P10">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="Q10">
-        <v>0.2286</v>
+        <v>0.1923</v>
       </c>
       <c r="R10">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1884</v>
+        <v>0.2233</v>
       </c>
       <c r="U10">
-        <v>0.1897</v>
+        <v>0.1872</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2163</v>
+        <v>0.2141</v>
       </c>
       <c r="X10">
         <v>0.2227</v>
       </c>
       <c r="Y10">
-        <v>0.9907</v>
+        <v>0.9815</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1590,22 +1686,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2154</v>
+        <v>0.1974</v>
       </c>
       <c r="AG10">
-        <v>0.846</v>
+        <v>1.003</v>
       </c>
       <c r="AH10">
         <v>0.2</v>
       </c>
       <c r="AM10">
-        <v>4.14</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1615,17 +1711,26 @@
       <c r="B11" t="s">
         <v>60</v>
       </c>
+      <c r="C11">
+        <v>5.5</v>
+      </c>
+      <c r="D11">
+        <v>-103</v>
+      </c>
+      <c r="E11">
+        <v>-120</v>
+      </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>823096</v>
+        <v>823825</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1634,46 +1739,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>0.3008</v>
+        <v>0.2185</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="P11">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="Q11">
-        <v>0.3088</v>
+        <v>0.2273</v>
       </c>
       <c r="R11">
-        <v>0.405</v>
+        <v>0.398</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2343</v>
+        <v>0.2122</v>
       </c>
       <c r="U11">
-        <v>0.216</v>
+        <v>0.2002</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2428</v>
+        <v>0.211</v>
       </c>
       <c r="X11">
         <v>0.2227</v>
       </c>
       <c r="Y11">
-        <v>0.9826</v>
+        <v>0.9666</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1682,22 +1787,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AE11" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.304</v>
+        <v>0.222</v>
       </c>
       <c r="AG11">
-        <v>1.052</v>
+        <v>0.9528</v>
       </c>
       <c r="AH11">
-        <v>-0.91</v>
+        <v>0.2</v>
       </c>
       <c r="AM11">
-        <v>6.89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1705,19 +1810,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>-122</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
       <c r="G12">
-        <v>823096</v>
+        <v>823584</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I12">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1726,46 +1840,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>0.2433</v>
+        <v>0.2346</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="P12">
-        <v>4.07</v>
+        <v>4.8</v>
       </c>
       <c r="Q12">
-        <v>0.2478</v>
+        <v>0.2346</v>
       </c>
       <c r="R12">
-        <v>0.361</v>
+        <v>0.288</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1536</v>
+        <v>0.2227</v>
       </c>
       <c r="U12">
-        <v>0.1554</v>
+        <v>0.2218</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>0.2212</v>
+        <v>0.2144</v>
       </c>
       <c r="X12">
         <v>0.2227</v>
       </c>
       <c r="Y12">
-        <v>0.9613</v>
+        <v>1.0067</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1774,22 +1888,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.81</v>
+        <v>4.72</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2449</v>
+        <v>0.2346</v>
       </c>
       <c r="AG12">
-        <v>0.6899</v>
+        <v>1</v>
       </c>
       <c r="AH12">
         <v>0.2</v>
       </c>
       <c r="AM12">
-        <v>4.01</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1799,17 +1913,26 @@
       <c r="B13" t="s">
         <v>63</v>
       </c>
+      <c r="C13">
+        <v>4.5</v>
+      </c>
+      <c r="D13">
+        <v>-165</v>
+      </c>
+      <c r="E13">
+        <v>130</v>
+      </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>823825</v>
+        <v>823584</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1818,46 +1941,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>0.2185</v>
+        <v>0.2256</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="P13">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="Q13">
-        <v>0.2273</v>
+        <v>0.211</v>
       </c>
       <c r="R13">
-        <v>0.398</v>
+        <v>0.353</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2122</v>
+        <v>0.2304</v>
       </c>
       <c r="U13">
-        <v>0.2002</v>
+        <v>0.2222</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>0.211</v>
+        <v>0.2234</v>
       </c>
       <c r="X13">
         <v>0.2227</v>
       </c>
       <c r="Y13">
-        <v>0.9666</v>
+        <v>0.9914</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1866,22 +1989,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.222</v>
+        <v>0.2205</v>
       </c>
       <c r="AG13">
-        <v>0.9528</v>
+        <v>1.0348</v>
       </c>
       <c r="AH13">
         <v>0.2</v>
       </c>
       <c r="AM13">
-        <v>5</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1889,67 +2012,34 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14">
+        <v>4.5</v>
+      </c>
+      <c r="D14">
+        <v>124</v>
+      </c>
+      <c r="E14">
+        <v>-152</v>
+      </c>
+      <c r="F14" t="s">
         <v>65</v>
       </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>823825</v>
+      <c r="G14" t="s">
+        <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14">
-        <v>4</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0.2</v>
-      </c>
-      <c r="N14">
-        <v>5</v>
-      </c>
-      <c r="O14">
-        <v>104</v>
-      </c>
-      <c r="P14">
-        <v>4.42</v>
-      </c>
-      <c r="Q14">
-        <v>0.1923</v>
-      </c>
-      <c r="R14">
-        <v>0.342</v>
+        <v>2</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
-      </c>
-      <c r="T14">
-        <v>0.2233</v>
-      </c>
-      <c r="U14">
-        <v>0.1872</v>
-      </c>
-      <c r="V14">
-        <v>9</v>
-      </c>
-      <c r="W14">
-        <v>0.2141</v>
-      </c>
-      <c r="X14">
-        <v>0.2227</v>
-      </c>
-      <c r="Y14">
-        <v>0.9815</v>
+        <v>44</v>
+      </c>
+      <c r="V14" t="s">
+        <v>44</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1957,23 +2047,8 @@
       <c r="AC14" t="s">
         <v>44</v>
       </c>
-      <c r="AD14">
-        <v>3.46</v>
-      </c>
       <c r="AE14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF14">
-        <v>0.1974</v>
-      </c>
-      <c r="AG14">
-        <v>1.003</v>
-      </c>
-      <c r="AH14">
-        <v>0.2</v>
-      </c>
-      <c r="AM14">
-        <v>3.66</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1981,19 +2056,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="C15">
+        <v>4.5</v>
+      </c>
+      <c r="D15">
+        <v>-132</v>
+      </c>
+      <c r="E15">
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15">
-        <v>822692</v>
+        <v>824878</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2002,46 +2086,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>0.1893</v>
+        <v>0.2312</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="P15">
-        <v>4.41</v>
+        <v>4.25</v>
       </c>
       <c r="Q15">
-        <v>0.1416</v>
+        <v>0.2437</v>
       </c>
       <c r="R15">
-        <v>0.361</v>
+        <v>0.373</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2324</v>
+        <v>0.2281</v>
       </c>
       <c r="U15">
-        <v>0.2348</v>
+        <v>0.2246</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2065</v>
+        <v>0.2201</v>
       </c>
       <c r="X15">
         <v>0.2227</v>
       </c>
       <c r="Y15">
-        <v>1.0195</v>
+        <v>1.0026</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2050,22 +2134,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.81</v>
+        <v>5.43</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1721</v>
+        <v>0.2359</v>
       </c>
       <c r="AG15">
-        <v>1.0435</v>
+        <v>1.0242</v>
       </c>
       <c r="AH15">
         <v>0.2</v>
       </c>
       <c r="AM15">
-        <v>4.01</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2073,19 +2157,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+      <c r="D16">
+        <v>114</v>
+      </c>
+      <c r="E16">
+        <v>-132</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
       </c>
       <c r="G16">
-        <v>822692</v>
+        <v>824555</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2094,46 +2187,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>0.1834</v>
+        <v>0.2601</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="P16">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>0.1159</v>
+        <v>0.281</v>
       </c>
       <c r="R16">
-        <v>0.257</v>
+        <v>0.377</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2296</v>
+        <v>0.2261</v>
       </c>
       <c r="U16">
-        <v>0.2237</v>
+        <v>0.2473</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2196</v>
+        <v>0.2463</v>
       </c>
       <c r="X16">
         <v>0.2227</v>
       </c>
       <c r="Y16">
-        <v>0.9996</v>
+        <v>1.0271</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2142,22 +2235,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.56</v>
+        <v>6.41</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="AF16">
-        <v>0.1661</v>
+        <v>0.268</v>
       </c>
       <c r="AG16">
-        <v>1.0312</v>
+        <v>1.0154</v>
       </c>
       <c r="AH16">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM16">
-        <v>3.76</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2167,17 +2260,26 @@
       <c r="B17" t="s">
         <v>70</v>
       </c>
+      <c r="C17">
+        <v>5.5</v>
+      </c>
+      <c r="D17">
+        <v>-147</v>
+      </c>
+      <c r="E17">
+        <v>122</v>
+      </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G17">
-        <v>823506</v>
+        <v>824555</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2186,46 +2288,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>0.2326</v>
+        <v>0.2651</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="P17">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="Q17">
-        <v>0.2342</v>
+        <v>0.2456</v>
       </c>
       <c r="R17">
-        <v>0.357</v>
+        <v>0.363</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2541</v>
+        <v>0.2462</v>
       </c>
       <c r="U17">
-        <v>0.255</v>
+        <v>0.2408</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>0.2469</v>
+        <v>0.223</v>
       </c>
       <c r="X17">
         <v>0.2227</v>
       </c>
       <c r="Y17">
-        <v>0.9882</v>
+        <v>1.0349</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2234,22 +2336,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.17</v>
+        <v>6.63</v>
       </c>
       <c r="AE17" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="AF17">
-        <v>0.2332</v>
+        <v>0.258</v>
       </c>
       <c r="AG17">
-        <v>1.141</v>
+        <v>1.1057</v>
       </c>
       <c r="AH17">
         <v>-0.21</v>
       </c>
       <c r="AM17">
-        <v>5.96</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2257,19 +2359,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18">
+        <v>4.5</v>
+      </c>
+      <c r="D18">
+        <v>-108</v>
+      </c>
+      <c r="E18">
+        <v>-108</v>
+      </c>
+      <c r="F18" t="s">
         <v>72</v>
       </c>
-      <c r="F18" t="s">
-        <v>73</v>
-      </c>
       <c r="G18">
-        <v>822772</v>
+        <v>823015</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2278,46 +2389,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18">
-        <v>0.148</v>
+        <v>0.2198</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P18">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="Q18">
-        <v>0.1638</v>
+        <v>0.1727</v>
       </c>
       <c r="R18">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1929</v>
+        <v>0.2606</v>
       </c>
       <c r="U18">
-        <v>0.1805</v>
+        <v>0.2015</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.1891</v>
+        <v>0.215</v>
       </c>
       <c r="X18">
         <v>0.2227</v>
       </c>
       <c r="Y18">
-        <v>0.976</v>
+        <v>0.9503</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2326,22 +2437,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.87</v>
+        <v>5.3</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.1538</v>
+        <v>0.2031</v>
       </c>
       <c r="AG18">
-        <v>0.8663</v>
+        <v>1.1703</v>
       </c>
       <c r="AH18">
         <v>0.2</v>
       </c>
       <c r="AM18">
-        <v>3.07</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2349,19 +2460,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="C19">
+        <v>4.5</v>
+      </c>
+      <c r="D19">
+        <v>-104</v>
+      </c>
+      <c r="E19">
+        <v>-113</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G19">
-        <v>823584</v>
+        <v>823015</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2370,46 +2490,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>0.2256</v>
+        <v>0.1703</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P19">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="Q19">
-        <v>0.211</v>
+        <v>0.2019</v>
       </c>
       <c r="R19">
-        <v>0.353</v>
+        <v>0.342</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2304</v>
+        <v>0.2659</v>
       </c>
       <c r="U19">
-        <v>0.2222</v>
+        <v>0.2405</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2234</v>
+        <v>0.2371</v>
       </c>
       <c r="X19">
         <v>0.2227</v>
       </c>
       <c r="Y19">
-        <v>0.9914</v>
+        <v>1.0371</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2418,22 +2538,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.93</v>
+        <v>5.01</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2205</v>
+        <v>0.1811</v>
       </c>
       <c r="AG19">
-        <v>1.0348</v>
+        <v>1.1941</v>
       </c>
       <c r="AH19">
         <v>0.2</v>
       </c>
       <c r="AM19">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2441,67 +2561,34 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="C20">
+        <v>4.5</v>
+      </c>
+      <c r="D20">
+        <v>126</v>
+      </c>
+      <c r="E20">
+        <v>-162</v>
       </c>
       <c r="F20" t="s">
         <v>75</v>
       </c>
-      <c r="G20">
-        <v>823584</v>
+      <c r="G20" t="s">
+        <v>44</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20">
-        <v>4.2</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0.2346</v>
-      </c>
-      <c r="N20">
-        <v>4</v>
-      </c>
-      <c r="O20">
-        <v>81</v>
-      </c>
-      <c r="P20">
-        <v>4.8</v>
-      </c>
-      <c r="Q20">
-        <v>0.2346</v>
-      </c>
-      <c r="R20">
-        <v>0.288</v>
+        <v>3</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
-      </c>
-      <c r="T20">
-        <v>0.2227</v>
-      </c>
-      <c r="U20">
-        <v>0.2218</v>
-      </c>
-      <c r="V20">
-        <v>8</v>
-      </c>
-      <c r="W20">
-        <v>0.2144</v>
-      </c>
-      <c r="X20">
-        <v>0.2227</v>
-      </c>
-      <c r="Y20">
-        <v>1.0067</v>
+        <v>44</v>
+      </c>
+      <c r="V20" t="s">
+        <v>44</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2509,23 +2596,8 @@
       <c r="AC20" t="s">
         <v>44</v>
       </c>
-      <c r="AD20">
-        <v>4.72</v>
-      </c>
       <c r="AE20" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF20">
-        <v>0.2346</v>
-      </c>
-      <c r="AG20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>0.2</v>
-      </c>
-      <c r="AM20">
-        <v>4.92</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2533,19 +2605,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C21">
+        <v>5.5</v>
+      </c>
+      <c r="D21">
+        <v>-111</v>
+      </c>
+      <c r="E21">
+        <v>-113</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G21">
-        <v>824878</v>
+        <v>824963</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2554,46 +2635,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>0.2312</v>
+        <v>0.2475</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="P21">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="Q21">
-        <v>0.2437</v>
+        <v>0.2632</v>
       </c>
       <c r="R21">
-        <v>0.373</v>
+        <v>0.363</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2281</v>
+        <v>0.2504</v>
       </c>
       <c r="U21">
-        <v>0.2246</v>
+        <v>0.2308</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2201</v>
+        <v>0.2479</v>
       </c>
       <c r="X21">
         <v>0.2227</v>
       </c>
       <c r="Y21">
-        <v>1.0026</v>
+        <v>1.0329</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2602,22 +2683,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.43</v>
+        <v>6.67</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="AF21">
-        <v>0.2359</v>
+        <v>0.2532</v>
       </c>
       <c r="AG21">
-        <v>1.0242</v>
+        <v>1.1245</v>
       </c>
       <c r="AH21">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM21">
-        <v>5.63</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2625,19 +2706,19 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G22">
-        <v>824555</v>
+        <v>823988</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2649,43 +2730,43 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0.2601</v>
+        <v>0.2553</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="P22">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q22">
-        <v>0.281</v>
+        <v>0.3146</v>
       </c>
       <c r="R22">
-        <v>0.377</v>
+        <v>0.308</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2261</v>
+        <v>0.2482</v>
       </c>
       <c r="U22">
-        <v>0.2473</v>
+        <v>0.2411</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2463</v>
+        <v>0.2528</v>
       </c>
       <c r="X22">
         <v>0.2227</v>
       </c>
       <c r="Y22">
-        <v>1.0271</v>
+        <v>1.0373</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2694,22 +2775,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>6.41</v>
+        <v>6.61</v>
       </c>
       <c r="AE22" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="AF22">
-        <v>0.268</v>
+        <v>0.2736</v>
       </c>
       <c r="AG22">
-        <v>1.0154</v>
+        <v>1.1146</v>
       </c>
       <c r="AH22">
         <v>-0.21</v>
       </c>
       <c r="AM22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2717,19 +2798,19 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23">
-        <v>824555</v>
+        <v>823988</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2741,43 +2822,43 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0.2651</v>
+        <v>0.2047</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P23">
-        <v>4.08</v>
+        <v>4.52</v>
       </c>
       <c r="Q23">
-        <v>0.2456</v>
+        <v>0.2768</v>
       </c>
       <c r="R23">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2462</v>
+        <v>0.2046</v>
       </c>
       <c r="U23">
-        <v>0.2408</v>
+        <v>0.1828</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>0.223</v>
+        <v>0.2107</v>
       </c>
       <c r="X23">
         <v>0.2227</v>
       </c>
       <c r="Y23">
-        <v>1.0349</v>
+        <v>0.9381</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2786,22 +2867,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>6.63</v>
+        <v>4.23</v>
       </c>
       <c r="AE23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.258</v>
+        <v>0.2306</v>
       </c>
       <c r="AG23">
-        <v>1.1057</v>
+        <v>0.9186</v>
       </c>
       <c r="AH23">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM23">
-        <v>6.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2809,19 +2890,19 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G24">
-        <v>823015</v>
+        <v>823255</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2833,43 +2914,43 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.2198</v>
+        <v>0.2084</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P24">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="Q24">
-        <v>0.1727</v>
+        <v>0.2286</v>
       </c>
       <c r="R24">
-        <v>0.355</v>
+        <v>0.344</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2606</v>
+        <v>0.1884</v>
       </c>
       <c r="U24">
-        <v>0.2015</v>
+        <v>0.1897</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>0.215</v>
+        <v>0.2163</v>
       </c>
       <c r="X24">
         <v>0.2227</v>
       </c>
       <c r="Y24">
-        <v>0.9503</v>
+        <v>0.9907</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2878,22 +2959,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.3</v>
+        <v>3.94</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2031</v>
+        <v>0.2154</v>
       </c>
       <c r="AG24">
-        <v>1.1703</v>
+        <v>0.846</v>
       </c>
       <c r="AH24">
         <v>0.2</v>
       </c>
       <c r="AM24">
-        <v>5.5</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2901,19 +2982,19 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G25">
-        <v>823015</v>
+        <v>823255</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2925,43 +3006,43 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.1703</v>
+        <v>0.1486</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="P25">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="Q25">
-        <v>0.2019</v>
+        <v>0.0575</v>
       </c>
       <c r="R25">
-        <v>0.342</v>
+        <v>0.303</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2659</v>
+        <v>0.1963</v>
       </c>
       <c r="U25">
-        <v>0.2405</v>
+        <v>0.2281</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2371</v>
+        <v>0.2374</v>
       </c>
       <c r="X25">
         <v>0.2227</v>
       </c>
       <c r="Y25">
-        <v>1.0371</v>
+        <v>1.0127</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -2970,22 +3051,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>5.01</v>
+        <v>2.41</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1811</v>
+        <v>0.1263</v>
       </c>
       <c r="AG25">
-        <v>1.1941</v>
+        <v>0.8815</v>
       </c>
       <c r="AH25">
         <v>0.2</v>
       </c>
       <c r="AM25">
-        <v>5.21</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2993,19 +3074,19 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G26">
-        <v>824963</v>
+        <v>822692</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3017,43 +3098,43 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0.2475</v>
+        <v>0.1893</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P26">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="Q26">
-        <v>0.2632</v>
+        <v>0.1416</v>
       </c>
       <c r="R26">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2504</v>
+        <v>0.2324</v>
       </c>
       <c r="U26">
-        <v>0.2308</v>
+        <v>0.2348</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2479</v>
+        <v>0.2065</v>
       </c>
       <c r="X26">
         <v>0.2227</v>
       </c>
       <c r="Y26">
-        <v>1.0329</v>
+        <v>1.0195</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3062,22 +3143,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>6.67</v>
+        <v>3.81</v>
       </c>
       <c r="AE26" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.2532</v>
+        <v>0.1721</v>
       </c>
       <c r="AG26">
-        <v>1.1245</v>
+        <v>1.0435</v>
       </c>
       <c r="AH26">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM26">
-        <v>6.46</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3085,19 +3166,19 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G27">
-        <v>824963</v>
+        <v>822692</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3109,43 +3190,43 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.2126</v>
+        <v>0.1834</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O27">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="P27">
-        <v>4.19</v>
+        <v>4.57</v>
       </c>
       <c r="Q27">
-        <v>0.2066</v>
+        <v>0.1159</v>
       </c>
       <c r="R27">
-        <v>0.377</v>
+        <v>0.257</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
       </c>
       <c r="T27">
-        <v>0.1859</v>
+        <v>0.2296</v>
       </c>
       <c r="U27">
-        <v>0.1836</v>
+        <v>0.2237</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2083</v>
+        <v>0.2196</v>
       </c>
       <c r="X27">
         <v>0.2227</v>
       </c>
       <c r="Y27">
-        <v>0.99</v>
+        <v>0.9996</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3154,21 +3235,389 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.97</v>
+        <v>3.56</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.2104</v>
+        <v>0.1661</v>
       </c>
       <c r="AG27">
-        <v>0.8347</v>
+        <v>1.0312</v>
       </c>
       <c r="AH27">
         <v>0.2</v>
       </c>
       <c r="AM27">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28">
+        <v>823506</v>
+      </c>
+      <c r="H28" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28">
+        <v>5.6</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0.2326</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28">
+        <v>111</v>
+      </c>
+      <c r="P28">
+        <v>4.22</v>
+      </c>
+      <c r="Q28">
+        <v>0.2342</v>
+      </c>
+      <c r="R28">
+        <v>0.357</v>
+      </c>
+      <c r="S28" t="s">
+        <v>43</v>
+      </c>
+      <c r="T28">
+        <v>0.2541</v>
+      </c>
+      <c r="U28">
+        <v>0.255</v>
+      </c>
+      <c r="V28">
+        <v>9</v>
+      </c>
+      <c r="W28">
+        <v>0.2469</v>
+      </c>
+      <c r="X28">
+        <v>0.2227</v>
+      </c>
+      <c r="Y28">
+        <v>0.9882</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD28">
+        <v>6.17</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF28">
+        <v>0.2332</v>
+      </c>
+      <c r="AG28">
+        <v>1.141</v>
+      </c>
+      <c r="AH28">
+        <v>-0.21</v>
+      </c>
+      <c r="AM28">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29">
+        <v>822772</v>
+      </c>
+      <c r="H29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29">
+        <v>5.1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0.148</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29">
+        <v>116</v>
+      </c>
+      <c r="P29">
+        <v>4.29</v>
+      </c>
+      <c r="Q29">
+        <v>0.1638</v>
+      </c>
+      <c r="R29">
+        <v>0.367</v>
+      </c>
+      <c r="S29" t="s">
+        <v>43</v>
+      </c>
+      <c r="T29">
+        <v>0.1929</v>
+      </c>
+      <c r="U29">
+        <v>0.1805</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.1891</v>
+      </c>
+      <c r="X29">
+        <v>0.2227</v>
+      </c>
+      <c r="Y29">
+        <v>0.976</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD29">
+        <v>2.87</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF29">
+        <v>0.1538</v>
+      </c>
+      <c r="AG29">
+        <v>0.8663</v>
+      </c>
+      <c r="AH29">
+        <v>0.2</v>
+      </c>
+      <c r="AM29">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30">
+        <v>822772</v>
+      </c>
+      <c r="H30" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0.2253</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30">
+        <v>64</v>
+      </c>
+      <c r="P30">
+        <v>4.03</v>
+      </c>
+      <c r="Q30">
+        <v>0.1406</v>
+      </c>
+      <c r="R30">
+        <v>0.242</v>
+      </c>
+      <c r="S30" t="s">
+        <v>43</v>
+      </c>
+      <c r="T30">
+        <v>0.1676</v>
+      </c>
+      <c r="U30">
+        <v>0.1841</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>0.2075</v>
+      </c>
+      <c r="X30">
+        <v>0.2227</v>
+      </c>
+      <c r="Y30">
+        <v>0.9479</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30">
+        <v>1.77</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF30">
+        <v>0.2048</v>
+      </c>
+      <c r="AG30">
+        <v>0.7528</v>
+      </c>
+      <c r="AH30">
+        <v>0.2</v>
+      </c>
+      <c r="AM30">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31">
+        <v>824963</v>
+      </c>
+      <c r="H31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.2126</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>121</v>
+      </c>
+      <c r="P31">
+        <v>4.19</v>
+      </c>
+      <c r="Q31">
+        <v>0.2066</v>
+      </c>
+      <c r="R31">
+        <v>0.377</v>
+      </c>
+      <c r="S31" t="s">
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.1859</v>
+      </c>
+      <c r="U31">
+        <v>0.1836</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.2083</v>
+      </c>
+      <c r="X31">
+        <v>0.2227</v>
+      </c>
+      <c r="Y31">
+        <v>0.99</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31">
+        <v>3.97</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF31">
+        <v>0.2104</v>
+      </c>
+      <c r="AG31">
+        <v>0.8347</v>
+      </c>
+      <c r="AH31">
+        <v>0.2</v>
+      </c>
+      <c r="AM31">
         <v>4.17</v>
       </c>
     </row>

--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="95">
   <si>
     <t>date</t>
   </si>
@@ -142,24 +142,27 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Arizona Diamondbacks</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Arizona Diamondbacks</t>
-  </si>
-  <si>
     <t>Eduardo Rodriguez</t>
   </si>
   <si>
@@ -175,6 +178,18 @@
     <t>&gt;=7</t>
   </si>
   <si>
+    <t>Grayson Rodriguez</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
     <t>Bryan Woo</t>
   </si>
   <si>
@@ -184,6 +199,15 @@
     <t>Jesus Luzardo</t>
   </si>
   <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vasquez</t>
+  </si>
+  <si>
     <t>Ryan Gusto</t>
   </si>
   <si>
@@ -196,6 +220,27 @@
     <t>Sonny Gray</t>
   </si>
   <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Elmer Rodriguez</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Toronto Blue Jays</t>
+  </si>
+  <si>
     <t>Robert Stock</t>
   </si>
   <si>
@@ -220,9 +265,6 @@
     <t>Texas Rangers @ Chicago White Sox</t>
   </si>
   <si>
-    <t>6-7</t>
-  </si>
-  <si>
     <t>Sean Burke</t>
   </si>
   <si>
@@ -244,43 +286,7 @@
     <t>Connor Prielipp</t>
   </si>
   <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Grayson Rodriguez</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Randy Vásquez</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
     <t>Matt Waldron</t>
-  </si>
-  <si>
-    <t>Peter Lambert</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Toronto Blue Jays</t>
   </si>
   <si>
     <t>Spencer Miles</t>
@@ -670,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -806,10 +812,10 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-113</v>
+        <v>105</v>
       </c>
       <c r="E2">
-        <v>-111</v>
+        <v>-124</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -830,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>0.2146</v>
@@ -854,10 +860,10 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1698</v>
+        <v>0.191</v>
       </c>
       <c r="U2">
-        <v>0.1899</v>
+        <v>0.1861</v>
       </c>
       <c r="V2">
         <v>9</v>
@@ -866,10 +872,10 @@
         <v>0.2237</v>
       </c>
       <c r="X2">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y2">
-        <v>0.9702</v>
+        <v>0.9046</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -878,7 +884,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -887,13 +893,13 @@
         <v>0.2004</v>
       </c>
       <c r="AG2">
-        <v>0.7627</v>
+        <v>0.855</v>
       </c>
       <c r="AH2">
         <v>0.2</v>
       </c>
       <c r="AM2">
-        <v>3.63</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -910,7 +916,7 @@
         <v>-165</v>
       </c>
       <c r="E3">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -931,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>0.2141</v>
@@ -955,10 +961,10 @@
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.1617</v>
+        <v>0.1556</v>
       </c>
       <c r="U3">
-        <v>0.1575</v>
+        <v>0.1517</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -967,10 +973,10 @@
         <v>0.1877</v>
       </c>
       <c r="X3">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y3">
-        <v>0.8984</v>
+        <v>0.88</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -979,7 +985,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -988,13 +994,13 @@
         <v>0.2001</v>
       </c>
       <c r="AG3">
-        <v>0.7259</v>
+        <v>0.6964</v>
       </c>
       <c r="AH3">
         <v>0.2</v>
       </c>
       <c r="AM3">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1008,10 +1014,10 @@
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="E4">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -1032,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>0.1864</v>
@@ -1053,7 +1059,7 @@
         <v>0.403</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T4">
         <v>0.1711</v>
@@ -1068,10 +1074,10 @@
         <v>0.1756</v>
       </c>
       <c r="X4">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y4">
-        <v>0.9015</v>
+        <v>0.901</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1080,7 +1086,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1089,13 +1095,13 @@
         <v>0.159</v>
       </c>
       <c r="AG4">
-        <v>0.7684</v>
+        <v>0.7658</v>
       </c>
       <c r="AH4">
         <v>0.2</v>
       </c>
       <c r="AM4">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1103,7 +1109,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1112,7 +1118,7 @@
         <v>132</v>
       </c>
       <c r="E5">
-        <v>-143</v>
+        <v>-155</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -1133,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>0.1732</v>
@@ -1154,7 +1160,7 @@
         <v>0.394</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T5">
         <v>0.2106</v>
@@ -1169,10 +1175,10 @@
         <v>0.2171</v>
       </c>
       <c r="X5">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y5">
-        <v>0.9886</v>
+        <v>0.9872</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1181,7 +1187,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1190,13 +1196,13 @@
         <v>0.1777</v>
       </c>
       <c r="AG5">
-        <v>0.9458</v>
+        <v>0.9427</v>
       </c>
       <c r="AH5">
         <v>0.2</v>
       </c>
       <c r="AM5">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1204,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1213,10 +1219,10 @@
         <v>-125</v>
       </c>
       <c r="E6">
-        <v>-101</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>823180</v>
@@ -1234,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>0.1746</v>
@@ -1255,7 +1261,7 @@
         <v>0.349</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T6">
         <v>0.2297</v>
@@ -1270,10 +1276,10 @@
         <v>0.2345</v>
       </c>
       <c r="X6">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y6">
-        <v>0.972</v>
+        <v>0.9712</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1282,7 +1288,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1291,13 +1297,13 @@
         <v>0.1691</v>
       </c>
       <c r="AG6">
-        <v>1.0313</v>
+        <v>1.0279</v>
       </c>
       <c r="AH6">
         <v>0.2</v>
       </c>
       <c r="AM6">
-        <v>4.02</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1305,19 +1311,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-128</v>
+        <v>-122</v>
       </c>
       <c r="E7">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>823180</v>
@@ -1335,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>0.2265</v>
@@ -1356,7 +1362,7 @@
         <v>0.369</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T7">
         <v>0.3543</v>
@@ -1371,10 +1377,10 @@
         <v>0.2555</v>
       </c>
       <c r="X7">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y7">
-        <v>1.0302</v>
+        <v>1.0313</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1383,22 +1389,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="AE7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF7">
         <v>0.1965</v>
       </c>
       <c r="AG7">
-        <v>1.5909</v>
+        <v>1.5856</v>
       </c>
       <c r="AH7">
         <v>-0.91</v>
       </c>
       <c r="AM7">
-        <v>6.49</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1406,28 +1412,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
         <v>126</v>
       </c>
       <c r="E8">
-        <v>-162</v>
+        <v>-156</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>823096</v>
+        <v>823988</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,46 +1442,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>0.2433</v>
+        <v>0.2047</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P8">
-        <v>4.07</v>
+        <v>4.52</v>
       </c>
       <c r="Q8">
-        <v>0.2478</v>
+        <v>0.2768</v>
       </c>
       <c r="R8">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T8">
-        <v>0.1536</v>
+        <v>0.2087</v>
       </c>
       <c r="U8">
-        <v>0.1554</v>
+        <v>0.1872</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2212</v>
+        <v>0.211</v>
       </c>
       <c r="X8">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y8">
-        <v>0.9613</v>
+        <v>0.9386</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1484,22 +1490,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.81</v>
+        <v>4.3</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2449</v>
+        <v>0.2306</v>
       </c>
       <c r="AG8">
-        <v>0.6899</v>
+        <v>0.9341</v>
       </c>
       <c r="AH8">
         <v>0.2</v>
       </c>
       <c r="AM8">
-        <v>4.01</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1507,28 +1513,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>6.5</v>
       </c>
       <c r="D9">
-        <v>-162</v>
+        <v>-118</v>
       </c>
       <c r="E9">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>823096</v>
+        <v>823988</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1537,46 +1543,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>0.3008</v>
+        <v>0.2553</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="P9">
-        <v>4.13</v>
+        <v>4.33</v>
       </c>
       <c r="Q9">
-        <v>0.3088</v>
+        <v>0.3146</v>
       </c>
       <c r="R9">
-        <v>0.405</v>
+        <v>0.308</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T9">
-        <v>0.2343</v>
+        <v>0.2515</v>
       </c>
       <c r="U9">
-        <v>0.216</v>
+        <v>0.2452</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2428</v>
+        <v>0.2535</v>
       </c>
       <c r="X9">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y9">
-        <v>0.9826</v>
+        <v>1.038</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1585,22 +1591,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>7.8</v>
+        <v>6.68</v>
       </c>
       <c r="AE9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AF9">
-        <v>0.304</v>
+        <v>0.2736</v>
       </c>
       <c r="AG9">
-        <v>1.052</v>
+        <v>1.1255</v>
       </c>
       <c r="AH9">
-        <v>-0.91</v>
+        <v>-0.21</v>
       </c>
       <c r="AM9">
-        <v>6.89</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1608,28 +1614,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>-128</v>
+        <v>125</v>
       </c>
       <c r="E10">
-        <v>107</v>
+        <v>-153</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>823825</v>
+        <v>823096</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1638,46 +1644,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2</v>
+        <v>0.2433</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="P10">
-        <v>4.42</v>
+        <v>4.07</v>
       </c>
       <c r="Q10">
-        <v>0.1923</v>
+        <v>0.2478</v>
       </c>
       <c r="R10">
-        <v>0.342</v>
+        <v>0.361</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T10">
-        <v>0.2233</v>
+        <v>0.1536</v>
       </c>
       <c r="U10">
-        <v>0.1872</v>
+        <v>0.1554</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2141</v>
+        <v>0.2212</v>
       </c>
       <c r="X10">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y10">
-        <v>0.9815</v>
+        <v>0.9634</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1686,22 +1692,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.46</v>
+        <v>3.81</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1974</v>
+        <v>0.2449</v>
       </c>
       <c r="AG10">
-        <v>1.003</v>
+        <v>0.6876</v>
       </c>
       <c r="AH10">
         <v>0.2</v>
       </c>
       <c r="AM10">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1709,28 +1715,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D11">
         <v>-103</v>
       </c>
       <c r="E11">
-        <v>-120</v>
+        <v>-105</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>823825</v>
+        <v>823096</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1739,46 +1745,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2185</v>
+        <v>0.3008</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="P11">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="Q11">
-        <v>0.2273</v>
+        <v>0.3088</v>
       </c>
       <c r="R11">
-        <v>0.398</v>
+        <v>0.405</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T11">
-        <v>0.2122</v>
+        <v>0.2343</v>
       </c>
       <c r="U11">
-        <v>0.2002</v>
+        <v>0.216</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.211</v>
+        <v>0.2428</v>
       </c>
       <c r="X11">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y11">
-        <v>0.9666</v>
+        <v>0.9792</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1787,22 +1793,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>4.8</v>
+        <v>7.74</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="AF11">
-        <v>0.222</v>
+        <v>0.304</v>
       </c>
       <c r="AG11">
-        <v>0.9528</v>
+        <v>1.0485</v>
       </c>
       <c r="AH11">
-        <v>0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="AM11">
-        <v>5</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1810,28 +1816,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E12">
-        <v>-122</v>
+        <v>-135</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12">
-        <v>823584</v>
+        <v>823255</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1840,46 +1846,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2346</v>
+        <v>0.2084</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="P12">
-        <v>4.8</v>
+        <v>4.36</v>
       </c>
       <c r="Q12">
-        <v>0.2346</v>
+        <v>0.2286</v>
       </c>
       <c r="R12">
-        <v>0.288</v>
+        <v>0.344</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T12">
-        <v>0.2227</v>
+        <v>0.1884</v>
       </c>
       <c r="U12">
-        <v>0.2218</v>
+        <v>0.1897</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>0.2144</v>
+        <v>0.2163</v>
       </c>
       <c r="X12">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y12">
-        <v>1.0067</v>
+        <v>0.991</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1888,22 +1894,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.72</v>
+        <v>3.93</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2346</v>
+        <v>0.2154</v>
       </c>
       <c r="AG12">
-        <v>1</v>
+        <v>0.8432</v>
       </c>
       <c r="AH12">
         <v>0.2</v>
       </c>
       <c r="AM12">
-        <v>4.92</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1911,28 +1917,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13">
+        <v>3.5</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>-110</v>
+      </c>
+      <c r="F13" t="s">
         <v>63</v>
       </c>
-      <c r="C13">
-        <v>4.5</v>
-      </c>
-      <c r="D13">
-        <v>-165</v>
-      </c>
-      <c r="E13">
-        <v>130</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
       <c r="G13">
-        <v>823584</v>
+        <v>823255</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1941,46 +1947,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2256</v>
+        <v>0.1486</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="P13">
         <v>4.22</v>
       </c>
       <c r="Q13">
-        <v>0.211</v>
+        <v>0.0575</v>
       </c>
       <c r="R13">
-        <v>0.353</v>
+        <v>0.303</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T13">
-        <v>0.2304</v>
+        <v>0.1963</v>
       </c>
       <c r="U13">
-        <v>0.2222</v>
+        <v>0.2281</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
+        <v>0.2374</v>
+      </c>
+      <c r="X13">
         <v>0.2234</v>
       </c>
-      <c r="X13">
-        <v>0.2227</v>
-      </c>
       <c r="Y13">
-        <v>0.9914</v>
+        <v>1.0128</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1989,22 +1995,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.93</v>
+        <v>2.4</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2205</v>
+        <v>0.1263</v>
       </c>
       <c r="AG13">
-        <v>1.0348</v>
+        <v>0.8786</v>
       </c>
       <c r="AH13">
         <v>0.2</v>
       </c>
       <c r="AM13">
-        <v>5.13</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2012,34 +2018,76 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D14">
-        <v>124</v>
+        <v>-125</v>
       </c>
       <c r="E14">
-        <v>-152</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" t="s">
-        <v>44</v>
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>823825</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>67</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="M14">
+        <v>0.2</v>
+      </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14">
+        <v>104</v>
+      </c>
+      <c r="P14">
+        <v>4.42</v>
+      </c>
+      <c r="Q14">
+        <v>0.1923</v>
+      </c>
+      <c r="R14">
+        <v>0.342</v>
       </c>
       <c r="S14" t="s">
-        <v>44</v>
-      </c>
-      <c r="V14" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="T14">
+        <v>0.2233</v>
+      </c>
+      <c r="U14">
+        <v>0.1872</v>
+      </c>
+      <c r="V14">
+        <v>9</v>
+      </c>
+      <c r="W14">
+        <v>0.2141</v>
+      </c>
+      <c r="X14">
+        <v>0.2234</v>
+      </c>
+      <c r="Y14">
+        <v>0.9801</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2047,8 +2095,23 @@
       <c r="AC14" t="s">
         <v>44</v>
       </c>
+      <c r="AD14">
+        <v>3.44</v>
+      </c>
       <c r="AE14" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF14">
+        <v>0.1974</v>
+      </c>
+      <c r="AG14">
+        <v>0.9996</v>
+      </c>
+      <c r="AH14">
+        <v>0.2</v>
+      </c>
+      <c r="AM14">
+        <v>3.64</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2056,28 +2119,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15">
+        <v>5.5</v>
+      </c>
+      <c r="D15">
+        <v>-115</v>
+      </c>
+      <c r="E15">
+        <v>-104</v>
+      </c>
+      <c r="F15" t="s">
         <v>66</v>
       </c>
-      <c r="C15">
-        <v>4.5</v>
-      </c>
-      <c r="D15">
-        <v>-132</v>
-      </c>
-      <c r="E15">
-        <v>110</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
       <c r="G15">
-        <v>824878</v>
+        <v>823825</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2086,46 +2149,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2312</v>
+        <v>0.2185</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="P15">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="Q15">
-        <v>0.2437</v>
+        <v>0.2273</v>
       </c>
       <c r="R15">
-        <v>0.373</v>
+        <v>0.398</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T15">
-        <v>0.2281</v>
+        <v>0.2122</v>
       </c>
       <c r="U15">
-        <v>0.2246</v>
+        <v>0.2002</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2201</v>
+        <v>0.211</v>
       </c>
       <c r="X15">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y15">
-        <v>1.0026</v>
+        <v>0.9653</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2134,22 +2197,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.43</v>
+        <v>4.77</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2359</v>
+        <v>0.222</v>
       </c>
       <c r="AG15">
-        <v>1.0242</v>
+        <v>0.9496</v>
       </c>
       <c r="AH15">
         <v>0.2</v>
       </c>
       <c r="AM15">
-        <v>5.63</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2157,28 +2220,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
-        <v>114</v>
+        <v>-116</v>
       </c>
       <c r="E16">
-        <v>-132</v>
+        <v>-105</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G16">
-        <v>824555</v>
+        <v>822692</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2187,46 +2250,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>0.2601</v>
+        <v>0.1893</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="Q16">
-        <v>0.281</v>
+        <v>0.1416</v>
       </c>
       <c r="R16">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T16">
-        <v>0.2261</v>
+        <v>0.2324</v>
       </c>
       <c r="U16">
-        <v>0.2473</v>
+        <v>0.2348</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2463</v>
+        <v>0.2065</v>
       </c>
       <c r="X16">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y16">
-        <v>1.0271</v>
+        <v>1.0203</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2235,22 +2298,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.41</v>
+        <v>3.8</v>
       </c>
       <c r="AE16" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.268</v>
+        <v>0.1721</v>
       </c>
       <c r="AG16">
-        <v>1.0154</v>
+        <v>1.04</v>
       </c>
       <c r="AH16">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM16">
-        <v>6.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2258,28 +2321,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>5.5</v>
       </c>
       <c r="D17">
-        <v>-147</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>122</v>
+        <v>-152</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G17">
-        <v>824555</v>
+        <v>823506</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2288,46 +2351,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2651</v>
+        <v>0.2326</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P17">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="Q17">
-        <v>0.2456</v>
+        <v>0.2342</v>
       </c>
       <c r="R17">
-        <v>0.363</v>
+        <v>0.357</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T17">
-        <v>0.2462</v>
+        <v>0.2541</v>
       </c>
       <c r="U17">
-        <v>0.2408</v>
+        <v>0.255</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>0.223</v>
+        <v>0.2469</v>
       </c>
       <c r="X17">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y17">
-        <v>1.0349</v>
+        <v>0.9876</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2336,22 +2399,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.63</v>
+        <v>6.14</v>
       </c>
       <c r="AE17" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="AF17">
-        <v>0.258</v>
+        <v>0.2332</v>
       </c>
       <c r="AG17">
-        <v>1.1057</v>
+        <v>1.1371</v>
       </c>
       <c r="AH17">
         <v>-0.21</v>
       </c>
       <c r="AM17">
-        <v>6.42</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2359,28 +2422,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D18">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="E18">
-        <v>-108</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
         <v>72</v>
       </c>
       <c r="G18">
-        <v>823015</v>
+        <v>823506</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="I18">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2389,46 +2452,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2198</v>
+        <v>0.1205</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="P18">
-        <v>4.23</v>
+        <v>4.8</v>
       </c>
       <c r="Q18">
-        <v>0.1727</v>
+        <v>0.1205</v>
       </c>
       <c r="R18">
-        <v>0.355</v>
+        <v>0.293</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T18">
-        <v>0.2606</v>
+        <v>0.2183</v>
       </c>
       <c r="U18">
-        <v>0.2015</v>
+        <v>0.211</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>0.215</v>
+        <v>0.2188</v>
       </c>
       <c r="X18">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y18">
-        <v>0.9503</v>
+        <v>1.0013</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2437,22 +2500,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2031</v>
+        <v>0.1205</v>
       </c>
       <c r="AG18">
-        <v>1.1703</v>
+        <v>0.9769</v>
       </c>
       <c r="AH18">
         <v>0.2</v>
       </c>
       <c r="AM18">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2460,28 +2523,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D19">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="E19">
-        <v>-113</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>823015</v>
+        <v>822772</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2490,46 +2553,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>0.1703</v>
+        <v>0.148</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="P19">
-        <v>4.06</v>
+        <v>4.29</v>
       </c>
       <c r="Q19">
-        <v>0.2019</v>
+        <v>0.1638</v>
       </c>
       <c r="R19">
-        <v>0.342</v>
+        <v>0.367</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T19">
-        <v>0.2659</v>
+        <v>0.1929</v>
       </c>
       <c r="U19">
-        <v>0.2405</v>
+        <v>0.1805</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2371</v>
+        <v>0.1891</v>
       </c>
       <c r="X19">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y19">
-        <v>1.0371</v>
+        <v>0.9774</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2538,22 +2601,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.01</v>
+        <v>2.86</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1811</v>
+        <v>0.1538</v>
       </c>
       <c r="AG19">
-        <v>1.1941</v>
+        <v>0.8634</v>
       </c>
       <c r="AH19">
         <v>0.2</v>
       </c>
       <c r="AM19">
-        <v>5.21</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2561,34 +2624,76 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>4.5</v>
       </c>
       <c r="D20">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E20">
-        <v>-162</v>
+        <v>-129</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" t="s">
-        <v>44</v>
+        <v>77</v>
+      </c>
+      <c r="G20">
+        <v>823584</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>67</v>
+      </c>
+      <c r="I20">
+        <v>4.2</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M20">
+        <v>0.2346</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>81</v>
+      </c>
+      <c r="P20">
+        <v>4.8</v>
+      </c>
+      <c r="Q20">
+        <v>0.2346</v>
+      </c>
+      <c r="R20">
+        <v>0.288</v>
       </c>
       <c r="S20" t="s">
-        <v>44</v>
-      </c>
-      <c r="V20" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="T20">
+        <v>0.2227</v>
+      </c>
+      <c r="U20">
+        <v>0.2218</v>
+      </c>
+      <c r="V20">
+        <v>8</v>
+      </c>
+      <c r="W20">
+        <v>0.2144</v>
+      </c>
+      <c r="X20">
+        <v>0.2234</v>
+      </c>
+      <c r="Y20">
+        <v>1.0053</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2596,8 +2701,23 @@
       <c r="AC20" t="s">
         <v>44</v>
       </c>
+      <c r="AD20">
+        <v>4.7</v>
+      </c>
       <c r="AE20" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF20">
+        <v>0.2346</v>
+      </c>
+      <c r="AG20">
+        <v>0.9967</v>
+      </c>
+      <c r="AH20">
+        <v>0.2</v>
+      </c>
+      <c r="AM20">
+        <v>4.9</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2605,22 +2725,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-111</v>
+        <v>-123</v>
       </c>
       <c r="E21">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21">
-        <v>824963</v>
+        <v>823584</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
@@ -2635,46 +2755,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2475</v>
+        <v>0.2256</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="P21">
-        <v>4.36</v>
+        <v>4.22</v>
       </c>
       <c r="Q21">
-        <v>0.2632</v>
+        <v>0.211</v>
       </c>
       <c r="R21">
-        <v>0.363</v>
+        <v>0.353</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T21">
-        <v>0.2504</v>
+        <v>0.2304</v>
       </c>
       <c r="U21">
-        <v>0.2308</v>
+        <v>0.2222</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2479</v>
+        <v>0.2234</v>
       </c>
       <c r="X21">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y21">
-        <v>1.0329</v>
+        <v>0.99</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2683,22 +2803,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>6.67</v>
+        <v>4.91</v>
       </c>
       <c r="AE21" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2532</v>
+        <v>0.2205</v>
       </c>
       <c r="AG21">
-        <v>1.1245</v>
+        <v>1.0313</v>
       </c>
       <c r="AH21">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM21">
-        <v>6.46</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2706,67 +2826,34 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="C22">
+        <v>4.5</v>
+      </c>
+      <c r="D22">
+        <v>130</v>
+      </c>
+      <c r="E22">
+        <v>-155</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22">
-        <v>823988</v>
+        <v>80</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22">
-        <v>4.8</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0.2553</v>
-      </c>
-      <c r="N22">
-        <v>5</v>
-      </c>
-      <c r="O22">
-        <v>89</v>
-      </c>
-      <c r="P22">
-        <v>4.33</v>
-      </c>
-      <c r="Q22">
-        <v>0.3146</v>
-      </c>
-      <c r="R22">
-        <v>0.308</v>
+        <v>4</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
-      </c>
-      <c r="T22">
-        <v>0.2482</v>
-      </c>
-      <c r="U22">
-        <v>0.2411</v>
-      </c>
-      <c r="V22">
-        <v>9</v>
-      </c>
-      <c r="W22">
-        <v>0.2528</v>
-      </c>
-      <c r="X22">
-        <v>0.2227</v>
-      </c>
-      <c r="Y22">
-        <v>1.0373</v>
+        <v>44</v>
+      </c>
+      <c r="V22" t="s">
+        <v>44</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2774,23 +2861,8 @@
       <c r="AC22" t="s">
         <v>44</v>
       </c>
-      <c r="AD22">
-        <v>6.61</v>
-      </c>
       <c r="AE22" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF22">
-        <v>0.2736</v>
-      </c>
-      <c r="AG22">
-        <v>1.1146</v>
-      </c>
-      <c r="AH22">
-        <v>-0.21</v>
-      </c>
-      <c r="AM22">
-        <v>6.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2798,19 +2870,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="C23">
+        <v>4.5</v>
+      </c>
+      <c r="D23">
+        <v>-164</v>
+      </c>
+      <c r="E23">
+        <v>128</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G23">
-        <v>823988</v>
+        <v>824878</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2819,46 +2900,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>0.2047</v>
+        <v>0.2312</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="P23">
-        <v>4.52</v>
+        <v>4.25</v>
       </c>
       <c r="Q23">
-        <v>0.2768</v>
+        <v>0.2437</v>
       </c>
       <c r="R23">
-        <v>0.359</v>
+        <v>0.373</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T23">
-        <v>0.2046</v>
+        <v>0.2281</v>
       </c>
       <c r="U23">
-        <v>0.1828</v>
+        <v>0.2246</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2107</v>
+        <v>0.2201</v>
       </c>
       <c r="X23">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y23">
-        <v>0.9381</v>
+        <v>1.0008</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2867,22 +2948,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.23</v>
+        <v>5.4</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2306</v>
+        <v>0.2359</v>
       </c>
       <c r="AG23">
-        <v>0.9186</v>
+        <v>1.0208</v>
       </c>
       <c r="AH23">
         <v>0.2</v>
       </c>
       <c r="AM23">
-        <v>4.43</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2890,19 +2971,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="C24">
+        <v>6.5</v>
+      </c>
+      <c r="D24">
+        <v>120</v>
+      </c>
+      <c r="E24">
+        <v>-143</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24">
-        <v>823255</v>
+        <v>824555</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2911,46 +3001,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2084</v>
+        <v>0.2601</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="P24">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="Q24">
-        <v>0.2286</v>
+        <v>0.281</v>
       </c>
       <c r="R24">
-        <v>0.344</v>
+        <v>0.377</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T24">
-        <v>0.1884</v>
+        <v>0.2261</v>
       </c>
       <c r="U24">
-        <v>0.1897</v>
+        <v>0.2473</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2163</v>
+        <v>0.2463</v>
       </c>
       <c r="X24">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y24">
-        <v>0.9907</v>
+        <v>1.0274</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2959,22 +3049,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.94</v>
+        <v>6.39</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AF24">
-        <v>0.2154</v>
+        <v>0.268</v>
       </c>
       <c r="AG24">
-        <v>0.846</v>
+        <v>1.012</v>
       </c>
       <c r="AH24">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM24">
-        <v>4.14</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2982,19 +3072,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="C25">
+        <v>5.5</v>
+      </c>
+      <c r="D25">
+        <v>-143</v>
+      </c>
+      <c r="E25">
+        <v>120</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G25">
-        <v>823255</v>
+        <v>824555</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3003,46 +3102,46 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>0.1486</v>
+        <v>0.2651</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="P25">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="Q25">
-        <v>0.0575</v>
+        <v>0.2456</v>
       </c>
       <c r="R25">
-        <v>0.303</v>
+        <v>0.363</v>
       </c>
       <c r="S25" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T25">
-        <v>0.1963</v>
+        <v>0.2462</v>
       </c>
       <c r="U25">
-        <v>0.2281</v>
+        <v>0.2408</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>0.2374</v>
+        <v>0.223</v>
       </c>
       <c r="X25">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y25">
-        <v>1.0127</v>
+        <v>1.0338</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3051,22 +3150,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>2.41</v>
+        <v>6.6</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AF25">
-        <v>0.1263</v>
+        <v>0.258</v>
       </c>
       <c r="AG25">
-        <v>0.8815</v>
+        <v>1.102</v>
       </c>
       <c r="AH25">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM25">
-        <v>2.61</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3074,19 +3173,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="C26">
+        <v>4.5</v>
+      </c>
+      <c r="D26">
+        <v>-106</v>
+      </c>
+      <c r="E26">
+        <v>-110</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G26">
-        <v>822692</v>
+        <v>823015</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3095,46 +3203,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1893</v>
+        <v>0.2198</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P26">
-        <v>4.41</v>
+        <v>4.23</v>
       </c>
       <c r="Q26">
-        <v>0.1416</v>
+        <v>0.1727</v>
       </c>
       <c r="R26">
-        <v>0.361</v>
+        <v>0.355</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T26">
-        <v>0.2324</v>
+        <v>0.2606</v>
       </c>
       <c r="U26">
-        <v>0.2348</v>
+        <v>0.2015</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2065</v>
+        <v>0.215</v>
       </c>
       <c r="X26">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y26">
-        <v>1.0195</v>
+        <v>0.948</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3143,22 +3251,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.81</v>
+        <v>5.27</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1721</v>
+        <v>0.2031</v>
       </c>
       <c r="AG26">
-        <v>1.0435</v>
+        <v>1.1663</v>
       </c>
       <c r="AH26">
         <v>0.2</v>
       </c>
       <c r="AM26">
-        <v>4.01</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3166,19 +3274,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="C27">
+        <v>4.5</v>
+      </c>
+      <c r="D27">
+        <v>116</v>
+      </c>
+      <c r="E27">
+        <v>-137</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G27">
-        <v>822692</v>
+        <v>823015</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3187,46 +3304,46 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1834</v>
+        <v>0.1703</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="P27">
-        <v>4.57</v>
+        <v>4.06</v>
       </c>
       <c r="Q27">
-        <v>0.1159</v>
+        <v>0.2019</v>
       </c>
       <c r="R27">
-        <v>0.257</v>
+        <v>0.342</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T27">
-        <v>0.2296</v>
+        <v>0.2659</v>
       </c>
       <c r="U27">
-        <v>0.2237</v>
+        <v>0.2405</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2196</v>
+        <v>0.2371</v>
       </c>
       <c r="X27">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y27">
-        <v>0.9996</v>
+        <v>1.0358</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3235,22 +3352,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.56</v>
+        <v>4.98</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1661</v>
+        <v>0.1811</v>
       </c>
       <c r="AG27">
-        <v>1.0312</v>
+        <v>1.19</v>
       </c>
       <c r="AH27">
         <v>0.2</v>
       </c>
       <c r="AM27">
-        <v>3.76</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3258,67 +3375,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="C28">
+        <v>4.5</v>
+      </c>
+      <c r="D28">
+        <v>125</v>
+      </c>
+      <c r="E28">
+        <v>-143</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28">
-        <v>823506</v>
+        <v>89</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28">
-        <v>5.6</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0.2326</v>
-      </c>
-      <c r="N28">
-        <v>5</v>
-      </c>
-      <c r="O28">
-        <v>111</v>
-      </c>
-      <c r="P28">
-        <v>4.22</v>
-      </c>
-      <c r="Q28">
-        <v>0.2342</v>
-      </c>
-      <c r="R28">
-        <v>0.357</v>
+        <v>6</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
-      </c>
-      <c r="T28">
-        <v>0.2541</v>
-      </c>
-      <c r="U28">
-        <v>0.255</v>
-      </c>
-      <c r="V28">
-        <v>9</v>
-      </c>
-      <c r="W28">
-        <v>0.2469</v>
-      </c>
-      <c r="X28">
-        <v>0.2227</v>
-      </c>
-      <c r="Y28">
-        <v>0.9882</v>
+        <v>44</v>
+      </c>
+      <c r="V28" t="s">
+        <v>44</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3326,23 +3410,8 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
-      <c r="AD28">
-        <v>6.17</v>
-      </c>
       <c r="AE28" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF28">
-        <v>0.2332</v>
-      </c>
-      <c r="AG28">
-        <v>1.141</v>
-      </c>
-      <c r="AH28">
-        <v>-0.21</v>
-      </c>
-      <c r="AM28">
-        <v>5.96</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3350,19 +3419,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <v>5.5</v>
+      </c>
+      <c r="D29">
+        <v>-105</v>
+      </c>
+      <c r="E29">
+        <v>-115</v>
       </c>
       <c r="F29" t="s">
         <v>89</v>
       </c>
       <c r="G29">
-        <v>822772</v>
+        <v>824963</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3371,46 +3449,46 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>0.148</v>
+        <v>0.2475</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P29">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="Q29">
-        <v>0.1638</v>
+        <v>0.2632</v>
       </c>
       <c r="R29">
-        <v>0.367</v>
+        <v>0.363</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T29">
-        <v>0.1929</v>
+        <v>0.2504</v>
       </c>
       <c r="U29">
-        <v>0.1805</v>
+        <v>0.2308</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>0.1891</v>
+        <v>0.2479</v>
       </c>
       <c r="X29">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y29">
-        <v>0.976</v>
+        <v>1.0327</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3419,22 +3497,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>2.87</v>
+        <v>6.64</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AF29">
-        <v>0.1538</v>
+        <v>0.2532</v>
       </c>
       <c r="AG29">
-        <v>0.8663</v>
+        <v>1.1207</v>
       </c>
       <c r="AH29">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM29">
-        <v>3.07</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3442,67 +3520,67 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="G30">
-        <v>822772</v>
+        <v>822692</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="I30">
+        <v>4.6</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0.1834</v>
+      </c>
+      <c r="N30">
         <v>3</v>
       </c>
-      <c r="J30" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0.2253</v>
-      </c>
-      <c r="N30">
-        <v>4</v>
-      </c>
       <c r="O30">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P30">
-        <v>4.03</v>
+        <v>4.57</v>
       </c>
       <c r="Q30">
-        <v>0.1406</v>
+        <v>0.1159</v>
       </c>
       <c r="R30">
-        <v>0.242</v>
+        <v>0.257</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T30">
-        <v>0.1676</v>
+        <v>0.2296</v>
       </c>
       <c r="U30">
-        <v>0.1841</v>
+        <v>0.2237</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2075</v>
+        <v>0.2196</v>
       </c>
       <c r="X30">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y30">
-        <v>0.9479</v>
+        <v>1.0003</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3511,22 +3589,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>1.77</v>
+        <v>3.55</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
       </c>
       <c r="AF30">
-        <v>0.2048</v>
+        <v>0.1661</v>
       </c>
       <c r="AG30">
-        <v>0.7528</v>
+        <v>1.0277</v>
       </c>
       <c r="AH30">
         <v>0.2</v>
       </c>
       <c r="AM30">
-        <v>1.97</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3540,16 +3618,16 @@
         <v>75</v>
       </c>
       <c r="G31">
-        <v>824963</v>
+        <v>822772</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="I31">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -3558,43 +3636,43 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0.2126</v>
+        <v>0.2253</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="P31">
-        <v>4.19</v>
+        <v>4.03</v>
       </c>
       <c r="Q31">
-        <v>0.2066</v>
+        <v>0.1406</v>
       </c>
       <c r="R31">
-        <v>0.377</v>
+        <v>0.242</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T31">
-        <v>0.1859</v>
+        <v>0.1676</v>
       </c>
       <c r="U31">
-        <v>0.1836</v>
+        <v>0.1841</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
-        <v>0.2083</v>
+        <v>0.2075</v>
       </c>
       <c r="X31">
-        <v>0.2227</v>
+        <v>0.2234</v>
       </c>
       <c r="Y31">
-        <v>0.99</v>
+        <v>0.9491</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3603,22 +3681,114 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>3.97</v>
+        <v>1.76</v>
       </c>
       <c r="AE31" t="s">
         <v>45</v>
       </c>
       <c r="AF31">
-        <v>0.2104</v>
+        <v>0.2048</v>
       </c>
       <c r="AG31">
-        <v>0.8347</v>
+        <v>0.7503</v>
       </c>
       <c r="AH31">
         <v>0.2</v>
       </c>
       <c r="AM31">
-        <v>4.17</v>
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32">
+        <v>824963</v>
+      </c>
+      <c r="H32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32">
+        <v>5.4</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.2126</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32">
+        <v>121</v>
+      </c>
+      <c r="P32">
+        <v>4.19</v>
+      </c>
+      <c r="Q32">
+        <v>0.2066</v>
+      </c>
+      <c r="R32">
+        <v>0.377</v>
+      </c>
+      <c r="S32" t="s">
+        <v>49</v>
+      </c>
+      <c r="T32">
+        <v>0.1859</v>
+      </c>
+      <c r="U32">
+        <v>0.1836</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>0.2083</v>
+      </c>
+      <c r="X32">
+        <v>0.2234</v>
+      </c>
+      <c r="Y32">
+        <v>0.9889</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD32">
+        <v>3.95</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF32">
+        <v>0.2104</v>
+      </c>
+      <c r="AG32">
+        <v>0.8319</v>
+      </c>
+      <c r="AH32">
+        <v>0.2</v>
+      </c>
+      <c r="AM32">
+        <v>4.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -172,130 +172,133 @@
     <t>Cincinnati Reds @ San Francisco Giants</t>
   </si>
   <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Grayson Rodriguez</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vasquez</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Elmer Rodriguez</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ New York Mets</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>AJ Smith-Shawver</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>JT Ginn</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Matt Waldron</t>
+  </si>
+  <si>
+    <t>Spencer Miles</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
     <t>Landen Roupp</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Grayson Rodriguez</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Jesus Luzardo</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Randy Vasquez</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Peter Lambert</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Elmer Rodriguez</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ New York Mets</t>
-  </si>
-  <si>
-    <t>Dustin May</t>
-  </si>
-  <si>
-    <t>AJ Smith-Shawver</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>JT Ginn</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Matt Waldron</t>
-  </si>
-  <si>
-    <t>Spencer Miles</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
   </si>
 </sst>
 </file>
@@ -676,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -812,10 +815,10 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>-124</v>
+        <v>-120</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -872,7 +875,7 @@
         <v>0.2237</v>
       </c>
       <c r="X2">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y2">
         <v>0.9046</v>
@@ -884,7 +887,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -893,13 +896,13 @@
         <v>0.2004</v>
       </c>
       <c r="AG2">
-        <v>0.855</v>
+        <v>0.863</v>
       </c>
       <c r="AH2">
         <v>0.2</v>
       </c>
       <c r="AM2">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -916,7 +919,7 @@
         <v>-165</v>
       </c>
       <c r="E3">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -973,7 +976,7 @@
         <v>0.1877</v>
       </c>
       <c r="X3">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -985,7 +988,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -994,13 +997,13 @@
         <v>0.2001</v>
       </c>
       <c r="AG3">
-        <v>0.6964</v>
+        <v>0.7029</v>
       </c>
       <c r="AH3">
         <v>0.2</v>
       </c>
       <c r="AM3">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1017,7 +1020,7 @@
         <v>-120</v>
       </c>
       <c r="E4">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -1074,7 +1077,7 @@
         <v>0.1756</v>
       </c>
       <c r="X4">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y4">
         <v>0.901</v>
@@ -1086,7 +1089,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1095,13 +1098,13 @@
         <v>0.159</v>
       </c>
       <c r="AG4">
-        <v>0.7658</v>
+        <v>0.7729</v>
       </c>
       <c r="AH4">
         <v>0.2</v>
       </c>
       <c r="AM4">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1115,7 +1118,7 @@
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E5">
         <v>-155</v>
@@ -1175,7 +1178,7 @@
         <v>0.2171</v>
       </c>
       <c r="X5">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y5">
         <v>0.9872</v>
@@ -1187,7 +1190,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1196,13 +1199,13 @@
         <v>0.1777</v>
       </c>
       <c r="AG5">
-        <v>0.9427</v>
+        <v>0.9514</v>
       </c>
       <c r="AH5">
         <v>0.2</v>
       </c>
       <c r="AM5">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1219,7 +1222,7 @@
         <v>-125</v>
       </c>
       <c r="E6">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
@@ -1261,25 +1264,25 @@
         <v>0.349</v>
       </c>
       <c r="S6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2297</v>
+        <v>0.2602</v>
       </c>
       <c r="U6">
-        <v>0.2019</v>
+        <v>0.2395</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>0.2345</v>
       </c>
       <c r="X6">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y6">
-        <v>0.9712</v>
+        <v>0.9287</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1288,7 +1291,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1297,13 +1300,13 @@
         <v>0.1691</v>
       </c>
       <c r="AG6">
-        <v>1.0279</v>
+        <v>1.1754</v>
       </c>
       <c r="AH6">
         <v>0.2</v>
       </c>
       <c r="AM6">
-        <v>4</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1317,10 +1320,10 @@
         <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-122</v>
+        <v>-149</v>
       </c>
       <c r="E7">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F7" t="s">
         <v>52</v>
@@ -1332,7 +1335,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1341,34 +1344,34 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>0.2265</v>
+        <v>0.1938</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P7">
-        <v>4.26</v>
+        <v>4.08</v>
       </c>
       <c r="Q7">
-        <v>0.1453</v>
+        <v>0.2</v>
       </c>
       <c r="R7">
-        <v>0.369</v>
+        <v>0.365</v>
       </c>
       <c r="S7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.3543</v>
+        <v>0.2605</v>
       </c>
       <c r="U7">
-        <v>0.2809</v>
+        <v>0.2669</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1377,10 +1380,10 @@
         <v>0.2555</v>
       </c>
       <c r="X7">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y7">
-        <v>1.0313</v>
+        <v>1.0648</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1389,22 +1392,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>7.38</v>
+        <v>6.17</v>
       </c>
       <c r="AE7" t="s">
         <v>54</v>
       </c>
       <c r="AF7">
-        <v>0.1965</v>
+        <v>0.196</v>
       </c>
       <c r="AG7">
-        <v>1.5856</v>
+        <v>1.1767</v>
       </c>
       <c r="AH7">
-        <v>-0.91</v>
+        <v>-0.21</v>
       </c>
       <c r="AM7">
-        <v>6.47</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1418,7 +1421,7 @@
         <v>4.5</v>
       </c>
       <c r="D8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>-156</v>
@@ -1478,7 +1481,7 @@
         <v>0.211</v>
       </c>
       <c r="X8">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y8">
         <v>0.9386</v>
@@ -1490,7 +1493,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1499,13 +1502,13 @@
         <v>0.2306</v>
       </c>
       <c r="AG8">
-        <v>0.9341</v>
+        <v>0.9428</v>
       </c>
       <c r="AH8">
         <v>0.2</v>
       </c>
       <c r="AM8">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1579,7 +1582,7 @@
         <v>0.2535</v>
       </c>
       <c r="X9">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y9">
         <v>1.038</v>
@@ -1591,22 +1594,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>6.68</v>
+        <v>6.74</v>
       </c>
       <c r="AE9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AF9">
         <v>0.2736</v>
       </c>
       <c r="AG9">
-        <v>1.1255</v>
+        <v>1.136</v>
       </c>
       <c r="AH9">
         <v>-0.21</v>
       </c>
       <c r="AM9">
-        <v>6.47</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1614,7 +1617,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>5.5</v>
@@ -1626,7 +1629,7 @@
         <v>-153</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>823096</v>
@@ -1680,7 +1683,7 @@
         <v>0.2212</v>
       </c>
       <c r="X10">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y10">
         <v>0.9634</v>
@@ -1692,7 +1695,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1701,13 +1704,13 @@
         <v>0.2449</v>
       </c>
       <c r="AG10">
-        <v>0.6876</v>
+        <v>0.694</v>
       </c>
       <c r="AH10">
         <v>0.2</v>
       </c>
       <c r="AM10">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1715,7 +1718,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>7.5</v>
@@ -1727,7 +1730,7 @@
         <v>-105</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>823096</v>
@@ -1781,7 +1784,7 @@
         <v>0.2428</v>
       </c>
       <c r="X11">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y11">
         <v>0.9792</v>
@@ -1793,22 +1796,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>7.74</v>
+        <v>7.82</v>
       </c>
       <c r="AE11" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="AF11">
         <v>0.304</v>
       </c>
       <c r="AG11">
-        <v>1.0485</v>
+        <v>1.0583</v>
       </c>
       <c r="AH11">
         <v>-0.91</v>
       </c>
       <c r="AM11">
-        <v>6.83</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1822,10 +1825,10 @@
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>-135</v>
+        <v>-147</v>
       </c>
       <c r="F12" t="s">
         <v>63</v>
@@ -1867,25 +1870,25 @@
         <v>0.344</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1884</v>
+        <v>0.1897</v>
       </c>
       <c r="U12">
-        <v>0.1897</v>
+        <v>0.1903</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>0.2163</v>
       </c>
       <c r="X12">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y12">
-        <v>0.991</v>
+        <v>1.002</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1894,7 +1897,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.93</v>
+        <v>4.03</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1903,13 +1906,13 @@
         <v>0.2154</v>
       </c>
       <c r="AG12">
-        <v>0.8432</v>
+        <v>0.8568</v>
       </c>
       <c r="AH12">
         <v>0.2</v>
       </c>
       <c r="AM12">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1926,7 +1929,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>-110</v>
+        <v>-119</v>
       </c>
       <c r="F13" t="s">
         <v>63</v>
@@ -1983,7 +1986,7 @@
         <v>0.2374</v>
       </c>
       <c r="X13">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y13">
         <v>1.0128</v>
@@ -1995,7 +1998,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -2004,13 +2007,13 @@
         <v>0.1263</v>
       </c>
       <c r="AG13">
-        <v>0.8786</v>
+        <v>0.8868</v>
       </c>
       <c r="AH13">
         <v>0.2</v>
       </c>
       <c r="AM13">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2084,7 +2087,7 @@
         <v>0.2141</v>
       </c>
       <c r="X14">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y14">
         <v>0.9801</v>
@@ -2096,7 +2099,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2105,13 +2108,13 @@
         <v>0.1974</v>
       </c>
       <c r="AG14">
-        <v>0.9996</v>
+        <v>1.0089</v>
       </c>
       <c r="AH14">
         <v>0.2</v>
       </c>
       <c r="AM14">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2125,10 +2128,10 @@
         <v>5.5</v>
       </c>
       <c r="D15">
-        <v>-115</v>
+        <v>-103</v>
       </c>
       <c r="E15">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
         <v>66</v>
@@ -2185,7 +2188,7 @@
         <v>0.211</v>
       </c>
       <c r="X15">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y15">
         <v>0.9653</v>
@@ -2197,7 +2200,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.77</v>
+        <v>4.82</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2206,13 +2209,13 @@
         <v>0.222</v>
       </c>
       <c r="AG15">
-        <v>0.9496</v>
+        <v>0.9585</v>
       </c>
       <c r="AH15">
         <v>0.2</v>
       </c>
       <c r="AM15">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2226,10 +2229,10 @@
         <v>3.5</v>
       </c>
       <c r="D16">
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="E16">
-        <v>-105</v>
+        <v>-103</v>
       </c>
       <c r="F16" t="s">
         <v>70</v>
@@ -2286,7 +2289,7 @@
         <v>0.2065</v>
       </c>
       <c r="X16">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y16">
         <v>1.0203</v>
@@ -2298,7 +2301,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2307,13 +2310,13 @@
         <v>0.1721</v>
       </c>
       <c r="AG16">
-        <v>1.04</v>
+        <v>1.0497</v>
       </c>
       <c r="AH16">
         <v>0.2</v>
       </c>
       <c r="AM16">
-        <v>4</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2327,10 +2330,10 @@
         <v>5.5</v>
       </c>
       <c r="D17">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E17">
-        <v>-152</v>
+        <v>-142</v>
       </c>
       <c r="F17" t="s">
         <v>72</v>
@@ -2387,7 +2390,7 @@
         <v>0.2469</v>
       </c>
       <c r="X17">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y17">
         <v>0.9876</v>
@@ -2399,22 +2402,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="AE17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AF17">
         <v>0.2332</v>
       </c>
       <c r="AG17">
-        <v>1.1371</v>
+        <v>1.1477</v>
       </c>
       <c r="AH17">
         <v>-0.21</v>
       </c>
       <c r="AM17">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2428,7 +2431,7 @@
         <v>3.5</v>
       </c>
       <c r="D18">
-        <v>-102</v>
+        <v>-113</v>
       </c>
       <c r="E18">
         <v>106</v>
@@ -2488,7 +2491,7 @@
         <v>0.2188</v>
       </c>
       <c r="X18">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y18">
         <v>1.0013</v>
@@ -2500,7 +2503,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2509,13 +2512,13 @@
         <v>0.1205</v>
       </c>
       <c r="AG18">
-        <v>0.9769</v>
+        <v>0.986</v>
       </c>
       <c r="AH18">
         <v>0.2</v>
       </c>
       <c r="AM18">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2532,7 +2535,7 @@
         <v>-113</v>
       </c>
       <c r="E19">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
         <v>75</v>
@@ -2589,7 +2592,7 @@
         <v>0.1891</v>
       </c>
       <c r="X19">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y19">
         <v>0.9774</v>
@@ -2601,7 +2604,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2610,13 +2613,13 @@
         <v>0.1538</v>
       </c>
       <c r="AG19">
-        <v>0.8634</v>
+        <v>0.8715</v>
       </c>
       <c r="AH19">
         <v>0.2</v>
       </c>
       <c r="AM19">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2690,7 +2693,7 @@
         <v>0.2144</v>
       </c>
       <c r="X20">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y20">
         <v>1.0053</v>
@@ -2702,7 +2705,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2711,13 +2714,13 @@
         <v>0.2346</v>
       </c>
       <c r="AG20">
-        <v>0.9967</v>
+        <v>1.006</v>
       </c>
       <c r="AH20">
         <v>0.2</v>
       </c>
       <c r="AM20">
-        <v>4.9</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2731,7 +2734,7 @@
         <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-123</v>
+        <v>-121</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -2791,7 +2794,7 @@
         <v>0.2234</v>
       </c>
       <c r="X21">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y21">
         <v>0.99</v>
@@ -2803,7 +2806,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.91</v>
+        <v>4.95</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2812,13 +2815,13 @@
         <v>0.2205</v>
       </c>
       <c r="AG21">
-        <v>1.0313</v>
+        <v>1.0409</v>
       </c>
       <c r="AH21">
         <v>0.2</v>
       </c>
       <c r="AM21">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2936,7 +2939,7 @@
         <v>0.2201</v>
       </c>
       <c r="X23">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y23">
         <v>1.0008</v>
@@ -2948,7 +2951,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2957,13 +2960,13 @@
         <v>0.2359</v>
       </c>
       <c r="AG23">
-        <v>1.0208</v>
+        <v>1.0303</v>
       </c>
       <c r="AH23">
         <v>0.2</v>
       </c>
       <c r="AM23">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3037,7 +3040,7 @@
         <v>0.2463</v>
       </c>
       <c r="X24">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y24">
         <v>1.0274</v>
@@ -3049,22 +3052,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>6.39</v>
+        <v>6.45</v>
       </c>
       <c r="AE24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AF24">
         <v>0.268</v>
       </c>
       <c r="AG24">
-        <v>1.012</v>
+        <v>1.0214</v>
       </c>
       <c r="AH24">
         <v>-0.21</v>
       </c>
       <c r="AM24">
-        <v>6.18</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3138,7 +3141,7 @@
         <v>0.223</v>
       </c>
       <c r="X25">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y25">
         <v>1.0338</v>
@@ -3150,22 +3153,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.6</v>
+        <v>6.66</v>
       </c>
       <c r="AE25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AF25">
         <v>0.258</v>
       </c>
       <c r="AG25">
-        <v>1.102</v>
+        <v>1.1123</v>
       </c>
       <c r="AH25">
         <v>-0.21</v>
       </c>
       <c r="AM25">
-        <v>6.39</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3239,7 +3242,7 @@
         <v>0.215</v>
       </c>
       <c r="X26">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y26">
         <v>0.948</v>
@@ -3251,7 +3254,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>5.27</v>
+        <v>5.32</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3260,13 +3263,13 @@
         <v>0.2031</v>
       </c>
       <c r="AG26">
-        <v>1.1663</v>
+        <v>1.1772</v>
       </c>
       <c r="AH26">
         <v>0.2</v>
       </c>
       <c r="AM26">
-        <v>5.47</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3280,7 +3283,7 @@
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E27">
         <v>-137</v>
@@ -3340,7 +3343,7 @@
         <v>0.2371</v>
       </c>
       <c r="X27">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y27">
         <v>1.0358</v>
@@ -3352,7 +3355,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3361,13 +3364,13 @@
         <v>0.1811</v>
       </c>
       <c r="AG27">
-        <v>1.19</v>
+        <v>1.2011</v>
       </c>
       <c r="AH27">
         <v>0.2</v>
       </c>
       <c r="AM27">
-        <v>5.18</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3384,7 +3387,7 @@
         <v>125</v>
       </c>
       <c r="E28">
-        <v>-143</v>
+        <v>-130</v>
       </c>
       <c r="F28" t="s">
         <v>89</v>
@@ -3428,7 +3431,7 @@
         <v>-105</v>
       </c>
       <c r="E29">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="F29" t="s">
         <v>89</v>
@@ -3485,7 +3488,7 @@
         <v>0.2479</v>
       </c>
       <c r="X29">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y29">
         <v>1.0327</v>
@@ -3497,22 +3500,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.64</v>
+        <v>6.7</v>
       </c>
       <c r="AE29" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AF29">
         <v>0.2532</v>
       </c>
       <c r="AG29">
-        <v>1.1207</v>
+        <v>1.1312</v>
       </c>
       <c r="AH29">
         <v>-0.21</v>
       </c>
       <c r="AM29">
-        <v>6.43</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3577,7 +3580,7 @@
         <v>0.2196</v>
       </c>
       <c r="X30">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y30">
         <v>1.0003</v>
@@ -3589,7 +3592,7 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
@@ -3598,13 +3601,13 @@
         <v>0.1661</v>
       </c>
       <c r="AG30">
-        <v>1.0277</v>
+        <v>1.0373</v>
       </c>
       <c r="AH30">
         <v>0.2</v>
       </c>
       <c r="AM30">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3669,7 +3672,7 @@
         <v>0.2075</v>
       </c>
       <c r="X31">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y31">
         <v>0.9491</v>
@@ -3681,7 +3684,7 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE31" t="s">
         <v>45</v>
@@ -3690,13 +3693,13 @@
         <v>0.2048</v>
       </c>
       <c r="AG31">
-        <v>0.7503</v>
+        <v>0.7573</v>
       </c>
       <c r="AH31">
         <v>0.2</v>
       </c>
       <c r="AM31">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3761,7 +3764,7 @@
         <v>0.2083</v>
       </c>
       <c r="X32">
-        <v>0.2234</v>
+        <v>0.2214</v>
       </c>
       <c r="Y32">
         <v>0.9889</v>
@@ -3773,7 +3776,7 @@
         <v>44</v>
       </c>
       <c r="AD32">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="AE32" t="s">
         <v>45</v>
@@ -3782,13 +3785,114 @@
         <v>0.2104</v>
       </c>
       <c r="AG32">
-        <v>0.8319</v>
+        <v>0.8397</v>
       </c>
       <c r="AH32">
         <v>0.2</v>
       </c>
       <c r="AM32">
-        <v>4.15</v>
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33">
+        <v>5.5</v>
+      </c>
+      <c r="D33">
+        <v>-122</v>
+      </c>
+      <c r="E33">
+        <v>102</v>
+      </c>
+      <c r="F33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33">
+        <v>823180</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33">
+        <v>5.4</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>6</v>
+      </c>
+      <c r="M33">
+        <v>0.2265</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>117</v>
+      </c>
+      <c r="P33">
+        <v>4.26</v>
+      </c>
+      <c r="Q33">
+        <v>0.1453</v>
+      </c>
+      <c r="R33">
+        <v>0.369</v>
+      </c>
+      <c r="S33" t="s">
+        <v>49</v>
+      </c>
+      <c r="T33">
+        <v>0.3543</v>
+      </c>
+      <c r="U33">
+        <v>0.2809</v>
+      </c>
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33">
+        <v>0.2555</v>
+      </c>
+      <c r="X33">
+        <v>0.2234</v>
+      </c>
+      <c r="Y33">
+        <v>1.0313</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD33">
+        <v>7.38</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF33">
+        <v>0.1965</v>
+      </c>
+      <c r="AG33">
+        <v>1.5856</v>
+      </c>
+      <c r="AH33">
+        <v>-0.91</v>
+      </c>
+      <c r="AM33">
+        <v>6.47</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -160,142 +160,142 @@
     <t>Chicago Cubs @ Arizona Diamondbacks</t>
   </si>
   <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Grayson Rodriguez</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vásquez</t>
+  </si>
+  <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Matt Waldron</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Elmer Rodríguez</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Spencer Miles</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ New York Mets</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Grayson Rodriguez</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Jesus Luzardo</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Randy Vasquez</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Peter Lambert</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Elmer Rodriguez</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Toronto Blue Jays</t>
-  </si>
-  <si>
     <t>Robert Stock</t>
   </si>
   <si>
-    <t>Milwaukee Brewers @ New York Mets</t>
-  </si>
-  <si>
-    <t>Dustin May</t>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
   </si>
   <si>
     <t>AJ Smith-Shawver</t>
   </si>
   <si>
-    <t>Los Angeles Dodgers @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
     <t>JT Ginn</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Matt Waldron</t>
-  </si>
-  <si>
-    <t>Spencer Miles</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
   </si>
   <si>
     <t>Landen Roupp</t>
@@ -842,7 +842,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>0.2146</v>
+        <v>0.2142</v>
       </c>
       <c r="N2">
         <v>5</v>
@@ -851,10 +851,10 @@
         <v>109</v>
       </c>
       <c r="P2">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q2">
-        <v>0.1743</v>
+        <v>0.1835</v>
       </c>
       <c r="R2">
         <v>0.353</v>
@@ -872,10 +872,10 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2237</v>
+        <v>0.2236</v>
       </c>
       <c r="X2">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y2">
         <v>0.9046</v>
@@ -893,10 +893,10 @@
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2004</v>
+        <v>0.2033</v>
       </c>
       <c r="AG2">
-        <v>0.863</v>
+        <v>0.8563</v>
       </c>
       <c r="AH2">
         <v>0.2</v>
@@ -931,7 +931,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>0.2141</v>
+        <v>0.2094</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P3">
         <v>3.94</v>
       </c>
       <c r="Q3">
-        <v>0.1765</v>
+        <v>0.1639</v>
       </c>
       <c r="R3">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -973,10 +973,10 @@
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.1877</v>
+        <v>0.187</v>
       </c>
       <c r="X3">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -988,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2001</v>
+        <v>0.1922</v>
       </c>
       <c r="AG3">
-        <v>0.7029</v>
+        <v>0.6974</v>
       </c>
       <c r="AH3">
         <v>0.2</v>
       </c>
       <c r="AM3">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1032,7 +1032,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1044,31 +1044,31 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1864</v>
+        <v>0.1896</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="P4">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="Q4">
-        <v>0.1185</v>
+        <v>0.1171</v>
       </c>
       <c r="R4">
-        <v>0.403</v>
+        <v>0.357</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1711</v>
+        <v>0.1942</v>
       </c>
       <c r="U4">
-        <v>0.1712</v>
+        <v>0.1826</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1077,10 +1077,10 @@
         <v>0.1756</v>
       </c>
       <c r="X4">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y4">
-        <v>0.901</v>
+        <v>0.88</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1089,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.159</v>
+        <v>0.1637</v>
       </c>
       <c r="AG4">
-        <v>0.7729</v>
+        <v>0.8703</v>
       </c>
       <c r="AH4">
         <v>0.2</v>
       </c>
       <c r="AM4">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1112,7 +1112,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1133,7 +1133,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1145,31 +1145,31 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.1732</v>
+        <v>0.176</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="P5">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="Q5">
-        <v>0.1846</v>
+        <v>0.2294</v>
       </c>
       <c r="R5">
-        <v>0.394</v>
+        <v>0.353</v>
       </c>
       <c r="S5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2106</v>
+        <v>0.2034</v>
       </c>
       <c r="U5">
-        <v>0.2082</v>
+        <v>0.1947</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1178,10 +1178,10 @@
         <v>0.2171</v>
       </c>
       <c r="X5">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y5">
-        <v>0.9872</v>
+        <v>0.8982</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1190,22 +1190,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.08</v>
+        <v>3.79</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1777</v>
+        <v>0.1948</v>
       </c>
       <c r="AG5">
-        <v>0.9514</v>
+        <v>0.9117</v>
       </c>
       <c r="AH5">
         <v>0.2</v>
       </c>
       <c r="AM5">
-        <v>4.28</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1213,7 +1213,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1225,7 +1225,7 @@
         <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>823180</v>
@@ -1234,7 +1234,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1246,22 +1246,22 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.1746</v>
+        <v>0.1725</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="P6">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="Q6">
-        <v>0.1589</v>
+        <v>0.1529</v>
       </c>
       <c r="R6">
-        <v>0.349</v>
+        <v>0.298</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1279,7 +1279,7 @@
         <v>0.2345</v>
       </c>
       <c r="X6">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y6">
         <v>0.9287</v>
@@ -1291,22 +1291,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.16</v>
+        <v>3.86</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1691</v>
+        <v>0.1667</v>
       </c>
       <c r="AG6">
-        <v>1.1754</v>
+        <v>1.1663</v>
       </c>
       <c r="AH6">
         <v>0.2</v>
       </c>
       <c r="AM6">
-        <v>4.36</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1314,7 +1314,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1326,7 +1326,7 @@
         <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>823180</v>
@@ -1335,7 +1335,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>0.1938</v>
+        <v>0.1955</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="Q7">
-        <v>0.2</v>
+        <v>0.2165</v>
       </c>
       <c r="R7">
-        <v>0.365</v>
+        <v>0.327</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1380,7 +1380,7 @@
         <v>0.2555</v>
       </c>
       <c r="X7">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y7">
         <v>1.0648</v>
@@ -1392,22 +1392,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.17</v>
+        <v>6.11</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF7">
-        <v>0.196</v>
+        <v>0.2024</v>
       </c>
       <c r="AG7">
-        <v>1.1767</v>
+        <v>1.1676</v>
       </c>
       <c r="AH7">
         <v>-0.21</v>
       </c>
       <c r="AM7">
-        <v>5.96</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1415,19 +1415,19 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+      <c r="D8">
+        <v>-118</v>
+      </c>
+      <c r="E8">
+        <v>110</v>
+      </c>
+      <c r="F8" t="s">
         <v>55</v>
-      </c>
-      <c r="C8">
-        <v>4.5</v>
-      </c>
-      <c r="D8">
-        <v>128</v>
-      </c>
-      <c r="E8">
-        <v>-156</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
       </c>
       <c r="G8">
         <v>823988</v>
@@ -1436,7 +1436,7 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1448,43 +1448,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.2047</v>
+        <v>0.2553</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="P8">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="Q8">
-        <v>0.2768</v>
+        <v>0.3146</v>
       </c>
       <c r="R8">
-        <v>0.359</v>
+        <v>0.308</v>
       </c>
       <c r="S8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2087</v>
+        <v>0.2719</v>
       </c>
       <c r="U8">
-        <v>0.1872</v>
+        <v>0.2781</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.211</v>
+        <v>0.2535</v>
       </c>
       <c r="X8">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y8">
-        <v>0.9386</v>
+        <v>1.0973</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1493,22 +1493,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.34</v>
+        <v>7.64</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AF8">
-        <v>0.2306</v>
+        <v>0.2736</v>
       </c>
       <c r="AG8">
-        <v>0.9428</v>
+        <v>1.2188</v>
       </c>
       <c r="AH8">
-        <v>0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="AM8">
-        <v>4.54</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1519,16 +1519,16 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>-118</v>
+        <v>128</v>
       </c>
       <c r="E9">
-        <v>110</v>
+        <v>-156</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>823988</v>
@@ -1537,7 +1537,7 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1549,43 +1549,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.2553</v>
+        <v>0.2047</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="P9">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="Q9">
-        <v>0.3146</v>
+        <v>0.2768</v>
       </c>
       <c r="R9">
-        <v>0.308</v>
+        <v>0.359</v>
       </c>
       <c r="S9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2515</v>
+        <v>0.1784</v>
       </c>
       <c r="U9">
-        <v>0.2452</v>
+        <v>0.1793</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2535</v>
+        <v>0.211</v>
       </c>
       <c r="X9">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y9">
-        <v>1.038</v>
+        <v>0.88</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1594,22 +1594,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>6.74</v>
+        <v>3.45</v>
       </c>
       <c r="AE9" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2736</v>
+        <v>0.2306</v>
       </c>
       <c r="AG9">
-        <v>1.136</v>
+        <v>0.7994</v>
       </c>
       <c r="AH9">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM9">
-        <v>6.53</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1620,25 +1620,25 @@
         <v>58</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D10">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>-153</v>
+        <v>-147</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
       </c>
       <c r="G10">
-        <v>823096</v>
+        <v>823255</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1650,43 +1650,43 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2433</v>
+        <v>0.2084</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="P10">
-        <v>4.07</v>
+        <v>4.36</v>
       </c>
       <c r="Q10">
-        <v>0.2478</v>
+        <v>0.2286</v>
       </c>
       <c r="R10">
-        <v>0.361</v>
+        <v>0.344</v>
       </c>
       <c r="S10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1536</v>
+        <v>0.1897</v>
       </c>
       <c r="U10">
-        <v>0.1554</v>
+        <v>0.1903</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2212</v>
+        <v>0.2163</v>
       </c>
       <c r="X10">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y10">
-        <v>0.9634</v>
+        <v>1.002</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1695,22 +1695,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2449</v>
+        <v>0.2154</v>
       </c>
       <c r="AG10">
-        <v>0.694</v>
+        <v>0.8502</v>
       </c>
       <c r="AH10">
         <v>0.2</v>
       </c>
       <c r="AM10">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1721,25 +1721,25 @@
         <v>60</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>-105</v>
+        <v>-119</v>
       </c>
       <c r="F11" t="s">
         <v>59</v>
       </c>
       <c r="G11">
-        <v>823096</v>
+        <v>823255</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1751,43 +1751,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.3008</v>
+        <v>0.1486</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="P11">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="Q11">
-        <v>0.3088</v>
+        <v>0.0575</v>
       </c>
       <c r="R11">
-        <v>0.405</v>
+        <v>0.303</v>
       </c>
       <c r="S11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2343</v>
+        <v>0.282</v>
       </c>
       <c r="U11">
-        <v>0.216</v>
+        <v>0.2728</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2428</v>
+        <v>0.2374</v>
       </c>
       <c r="X11">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y11">
-        <v>0.9792</v>
+        <v>1.0872</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1796,22 +1796,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>7.82</v>
+        <v>3.71</v>
       </c>
       <c r="AE11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.304</v>
+        <v>0.1263</v>
       </c>
       <c r="AG11">
-        <v>1.0583</v>
+        <v>1.2638</v>
       </c>
       <c r="AH11">
-        <v>-0.91</v>
+        <v>0.2</v>
       </c>
       <c r="AM11">
-        <v>6.91</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1819,28 +1819,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+      <c r="D12">
+        <v>-103</v>
+      </c>
+      <c r="E12">
+        <v>-105</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="C12">
-        <v>4.5</v>
-      </c>
-      <c r="D12">
-        <v>124</v>
-      </c>
-      <c r="E12">
-        <v>-147</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
       <c r="G12">
-        <v>823255</v>
+        <v>823096</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1852,43 +1852,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2084</v>
+        <v>0.3008</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="P12">
-        <v>4.36</v>
+        <v>4.13</v>
       </c>
       <c r="Q12">
-        <v>0.2286</v>
+        <v>0.3088</v>
       </c>
       <c r="R12">
-        <v>0.344</v>
+        <v>0.405</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1897</v>
+        <v>0.2943</v>
       </c>
       <c r="U12">
-        <v>0.1903</v>
+        <v>0.2687</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>0.2163</v>
+        <v>0.2428</v>
       </c>
       <c r="X12">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y12">
-        <v>1.002</v>
+        <v>0.926</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1897,22 +1897,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.03</v>
+        <v>9.21</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AF12">
-        <v>0.2154</v>
+        <v>0.304</v>
       </c>
       <c r="AG12">
-        <v>0.8568</v>
+        <v>1.319</v>
       </c>
       <c r="AH12">
-        <v>0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="AM12">
-        <v>4.23</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1920,28 +1920,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>-119</v>
+        <v>-153</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>823255</v>
+        <v>823096</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1953,43 +1953,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.1486</v>
+        <v>0.2433</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="P13">
-        <v>4.22</v>
+        <v>4.07</v>
       </c>
       <c r="Q13">
-        <v>0.0575</v>
+        <v>0.2478</v>
       </c>
       <c r="R13">
-        <v>0.303</v>
+        <v>0.361</v>
       </c>
       <c r="S13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1963</v>
+        <v>0.1536</v>
       </c>
       <c r="U13">
-        <v>0.2281</v>
+        <v>0.1554</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2374</v>
+        <v>0.2212</v>
       </c>
       <c r="X13">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y13">
-        <v>1.0128</v>
+        <v>0.9267</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1998,22 +1998,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>2.43</v>
+        <v>3.67</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.1263</v>
+        <v>0.2449</v>
       </c>
       <c r="AG13">
-        <v>0.8868</v>
+        <v>0.6886</v>
       </c>
       <c r="AH13">
         <v>0.2</v>
       </c>
       <c r="AM13">
-        <v>2.63</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2021,28 +2021,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14">
+        <v>5.5</v>
+      </c>
+      <c r="D14">
+        <v>-103</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14" t="s">
         <v>65</v>
-      </c>
-      <c r="C14">
-        <v>3.5</v>
-      </c>
-      <c r="D14">
-        <v>-125</v>
-      </c>
-      <c r="E14">
-        <v>117</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
       </c>
       <c r="G14">
         <v>823825</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2054,43 +2054,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2</v>
+        <v>0.2185</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="P14">
-        <v>4.42</v>
+        <v>4.06</v>
       </c>
       <c r="Q14">
-        <v>0.1923</v>
+        <v>0.2273</v>
       </c>
       <c r="R14">
-        <v>0.342</v>
+        <v>0.398</v>
       </c>
       <c r="S14" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2233</v>
+        <v>0.2122</v>
       </c>
       <c r="U14">
-        <v>0.1872</v>
+        <v>0.2002</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2141</v>
+        <v>0.211</v>
       </c>
       <c r="X14">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y14">
-        <v>0.9801</v>
+        <v>0.9306</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2099,22 +2099,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.48</v>
+        <v>4.61</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1974</v>
+        <v>0.222</v>
       </c>
       <c r="AG14">
-        <v>1.0089</v>
+        <v>0.9511</v>
       </c>
       <c r="AH14">
         <v>0.2</v>
       </c>
       <c r="AM14">
-        <v>3.68</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2122,28 +2122,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D15">
-        <v>-103</v>
+        <v>-125</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>823825</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2155,43 +2155,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2185</v>
+        <v>0.2</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="P15">
-        <v>4.06</v>
+        <v>4.42</v>
       </c>
       <c r="Q15">
-        <v>0.2273</v>
+        <v>0.1923</v>
       </c>
       <c r="R15">
-        <v>0.398</v>
+        <v>0.342</v>
       </c>
       <c r="S15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2122</v>
+        <v>0.164</v>
       </c>
       <c r="U15">
-        <v>0.2002</v>
+        <v>0.1754</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.211</v>
+        <v>0.2141</v>
       </c>
       <c r="X15">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y15">
-        <v>0.9653</v>
+        <v>0.9774</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2200,22 +2200,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.82</v>
+        <v>2.53</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.222</v>
+        <v>0.1974</v>
       </c>
       <c r="AG15">
-        <v>0.9585</v>
+        <v>0.7349</v>
       </c>
       <c r="AH15">
         <v>0.2</v>
       </c>
       <c r="AM15">
-        <v>5.02</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2223,7 +2223,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2235,7 +2235,7 @@
         <v>-103</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>822692</v>
@@ -2274,13 +2274,13 @@
         <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2324</v>
+        <v>0.2396</v>
       </c>
       <c r="U16">
-        <v>0.2348</v>
+        <v>0.2402</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2289,10 +2289,10 @@
         <v>0.2065</v>
       </c>
       <c r="X16">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y16">
-        <v>1.0203</v>
+        <v>1.0387</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2301,7 +2301,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2310,13 +2310,13 @@
         <v>0.1721</v>
       </c>
       <c r="AG16">
-        <v>1.0497</v>
+        <v>1.074</v>
       </c>
       <c r="AH16">
         <v>0.2</v>
       </c>
       <c r="AM16">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2324,28 +2324,19 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17">
-        <v>5.5</v>
-      </c>
-      <c r="D17">
-        <v>124</v>
-      </c>
-      <c r="E17">
-        <v>-142</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G17">
-        <v>823506</v>
+        <v>822692</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2354,46 +2345,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>0.2326</v>
+        <v>0.1834</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O17">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="P17">
-        <v>4.22</v>
+        <v>4.57</v>
       </c>
       <c r="Q17">
-        <v>0.2342</v>
+        <v>0.1159</v>
       </c>
       <c r="R17">
-        <v>0.357</v>
+        <v>0.257</v>
       </c>
       <c r="S17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2541</v>
+        <v>0.2446</v>
       </c>
       <c r="U17">
-        <v>0.255</v>
+        <v>0.2343</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2469</v>
+        <v>0.2196</v>
       </c>
       <c r="X17">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y17">
-        <v>0.9876</v>
+        <v>1.0263</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2402,22 +2393,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.2</v>
+        <v>3.89</v>
       </c>
       <c r="AE17" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2332</v>
+        <v>0.1661</v>
       </c>
       <c r="AG17">
-        <v>1.1477</v>
+        <v>1.0962</v>
       </c>
       <c r="AH17">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM17">
-        <v>5.99</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2425,16 +2416,16 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D18">
-        <v>-113</v>
+        <v>124</v>
       </c>
       <c r="E18">
-        <v>106</v>
+        <v>-142</v>
       </c>
       <c r="F18" t="s">
         <v>72</v>
@@ -2443,10 +2434,10 @@
         <v>823506</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2458,43 +2449,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1205</v>
+        <v>0.2326</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="P18">
-        <v>4.8</v>
+        <v>4.22</v>
       </c>
       <c r="Q18">
-        <v>0.1205</v>
+        <v>0.2342</v>
       </c>
       <c r="R18">
-        <v>0.293</v>
+        <v>0.357</v>
       </c>
       <c r="S18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2183</v>
+        <v>0.2552</v>
       </c>
       <c r="U18">
-        <v>0.211</v>
+        <v>0.2569</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2188</v>
+        <v>0.2469</v>
       </c>
       <c r="X18">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y18">
-        <v>1.0013</v>
+        <v>0.9712</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2503,22 +2494,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.43</v>
+        <v>6.08</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF18">
-        <v>0.1205</v>
+        <v>0.2332</v>
       </c>
       <c r="AG18">
-        <v>0.986</v>
+        <v>1.1439</v>
       </c>
       <c r="AH18">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM18">
-        <v>2.63</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2526,28 +2517,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D19">
         <v>-113</v>
       </c>
       <c r="E19">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G19">
-        <v>822772</v>
+        <v>823506</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="I19">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2559,43 +2550,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.148</v>
+        <v>0.1205</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="P19">
-        <v>4.29</v>
+        <v>4.8</v>
       </c>
       <c r="Q19">
-        <v>0.1638</v>
+        <v>0.1205</v>
       </c>
       <c r="R19">
-        <v>0.367</v>
+        <v>0.293</v>
       </c>
       <c r="S19" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.1929</v>
+        <v>0.226</v>
       </c>
       <c r="U19">
-        <v>0.1805</v>
+        <v>0.2183</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.1891</v>
+        <v>0.2188</v>
       </c>
       <c r="X19">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y19">
-        <v>0.9774</v>
+        <v>0.9926</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2604,22 +2595,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1538</v>
+        <v>0.1205</v>
       </c>
       <c r="AG19">
-        <v>0.8715</v>
+        <v>1.0129</v>
       </c>
       <c r="AH19">
         <v>0.2</v>
       </c>
       <c r="AM19">
-        <v>3.09</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2627,28 +2618,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D20">
-        <v>124</v>
+        <v>-113</v>
       </c>
       <c r="E20">
-        <v>-129</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G20">
-        <v>823584</v>
+        <v>822772</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="I20">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2660,43 +2651,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2346</v>
+        <v>0.148</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>4.29</v>
       </c>
       <c r="Q20">
-        <v>0.2346</v>
+        <v>0.1638</v>
       </c>
       <c r="R20">
-        <v>0.288</v>
+        <v>0.367</v>
       </c>
       <c r="S20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2227</v>
+        <v>0.1759</v>
       </c>
       <c r="U20">
-        <v>0.2218</v>
+        <v>0.1694</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2144</v>
+        <v>0.1891</v>
       </c>
       <c r="X20">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y20">
-        <v>1.0053</v>
+        <v>0.9603</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2705,22 +2696,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.74</v>
+        <v>2.57</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2346</v>
+        <v>0.1538</v>
       </c>
       <c r="AG20">
-        <v>1.006</v>
+        <v>0.7883</v>
       </c>
       <c r="AH20">
         <v>0.2</v>
       </c>
       <c r="AM20">
-        <v>4.94</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2728,76 +2719,67 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21">
-        <v>4.5</v>
-      </c>
-      <c r="D21">
-        <v>-121</v>
-      </c>
-      <c r="E21">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21">
+        <v>822772</v>
+      </c>
+      <c r="H21" t="s">
         <v>77</v>
       </c>
-      <c r="G21">
-        <v>823584</v>
-      </c>
-      <c r="H21" t="s">
-        <v>42</v>
-      </c>
       <c r="I21">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>0.2256</v>
+        <v>0.2253</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="P21">
-        <v>4.22</v>
+        <v>4.03</v>
       </c>
       <c r="Q21">
-        <v>0.211</v>
+        <v>0.1406</v>
       </c>
       <c r="R21">
-        <v>0.353</v>
+        <v>0.242</v>
       </c>
       <c r="S21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2304</v>
+        <v>0.1817</v>
       </c>
       <c r="U21">
-        <v>0.2222</v>
+        <v>0.1923</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2234</v>
+        <v>0.2075</v>
       </c>
       <c r="X21">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y21">
-        <v>0.99</v>
+        <v>0.9489</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2806,22 +2788,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.95</v>
+        <v>1.92</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2205</v>
+        <v>0.2048</v>
       </c>
       <c r="AG21">
-        <v>1.0409</v>
+        <v>0.8146</v>
       </c>
       <c r="AH21">
         <v>0.2</v>
       </c>
       <c r="AM21">
-        <v>5.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2829,34 +2811,76 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>4.5</v>
       </c>
       <c r="D22">
-        <v>130</v>
+        <v>-121</v>
       </c>
       <c r="E22">
-        <v>-155</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22">
+        <v>823584</v>
+      </c>
+      <c r="H22" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22">
+        <v>5.2</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22">
+        <v>0.2256</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>109</v>
+      </c>
+      <c r="P22">
+        <v>4.22</v>
+      </c>
+      <c r="Q22">
+        <v>0.211</v>
+      </c>
+      <c r="R22">
+        <v>0.353</v>
+      </c>
+      <c r="S22" t="s">
         <v>80</v>
       </c>
-      <c r="G22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22">
-        <v>4</v>
-      </c>
-      <c r="S22" t="s">
-        <v>44</v>
-      </c>
-      <c r="V22" t="s">
-        <v>44</v>
+      <c r="T22">
+        <v>0.2304</v>
+      </c>
+      <c r="U22">
+        <v>0.2222</v>
+      </c>
+      <c r="V22">
+        <v>8</v>
+      </c>
+      <c r="W22">
+        <v>0.2234</v>
+      </c>
+      <c r="X22">
+        <v>0.2231</v>
+      </c>
+      <c r="Y22">
+        <v>0.99</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2864,8 +2888,23 @@
       <c r="AC22" t="s">
         <v>44</v>
       </c>
+      <c r="AD22">
+        <v>4.91</v>
+      </c>
       <c r="AE22" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF22">
+        <v>0.2205</v>
+      </c>
+      <c r="AG22">
+        <v>1.0329</v>
+      </c>
+      <c r="AH22">
+        <v>0.2</v>
+      </c>
+      <c r="AM22">
+        <v>5.11</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2879,22 +2918,22 @@
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>-164</v>
+        <v>124</v>
       </c>
       <c r="E23">
-        <v>128</v>
+        <v>-129</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>824878</v>
+        <v>823584</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="I23">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2903,46 +2942,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2312</v>
+        <v>0.2346</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="P23">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
-        <v>0.2437</v>
+        <v>0.2346</v>
       </c>
       <c r="R23">
-        <v>0.373</v>
+        <v>0.288</v>
       </c>
       <c r="S23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2281</v>
+        <v>0.2242</v>
       </c>
       <c r="U23">
-        <v>0.2246</v>
+        <v>0.2225</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>0.2201</v>
+        <v>0.2144</v>
       </c>
       <c r="X23">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y23">
-        <v>1.0008</v>
+        <v>0.9835</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2951,22 +2990,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.45</v>
+        <v>4.64</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2359</v>
+        <v>0.2346</v>
       </c>
       <c r="AG23">
-        <v>1.0303</v>
+        <v>1.0052</v>
       </c>
       <c r="AH23">
         <v>0.2</v>
       </c>
       <c r="AM23">
-        <v>5.65</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2977,25 +3016,25 @@
         <v>82</v>
       </c>
       <c r="C24">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>-164</v>
       </c>
       <c r="E24">
-        <v>-143</v>
+        <v>128</v>
       </c>
       <c r="F24" t="s">
         <v>83</v>
       </c>
       <c r="G24">
-        <v>824555</v>
+        <v>824878</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3004,46 +3043,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>0.2601</v>
+        <v>0.2312</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P24">
         <v>4.25</v>
       </c>
       <c r="Q24">
-        <v>0.281</v>
+        <v>0.2437</v>
       </c>
       <c r="R24">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="S24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2261</v>
+        <v>0.2348</v>
       </c>
       <c r="U24">
-        <v>0.2473</v>
+        <v>0.2252</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2463</v>
+        <v>0.2201</v>
       </c>
       <c r="X24">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y24">
-        <v>1.0274</v>
+        <v>0.9998</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3052,22 +3091,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>6.45</v>
+        <v>5.56</v>
       </c>
       <c r="AE24" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.268</v>
+        <v>0.2359</v>
       </c>
       <c r="AG24">
-        <v>1.0214</v>
+        <v>1.0526</v>
       </c>
       <c r="AH24">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AM24">
-        <v>6.24</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3078,16 +3117,16 @@
         <v>84</v>
       </c>
       <c r="C25">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D25">
+        <v>120</v>
+      </c>
+      <c r="E25">
         <v>-143</v>
       </c>
-      <c r="E25">
-        <v>120</v>
-      </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>824555</v>
@@ -3096,7 +3135,7 @@
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3108,43 +3147,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2651</v>
+        <v>0.2601</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="P25">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="Q25">
-        <v>0.2456</v>
+        <v>0.281</v>
       </c>
       <c r="R25">
-        <v>0.363</v>
+        <v>0.377</v>
       </c>
       <c r="S25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2462</v>
+        <v>0.2418</v>
       </c>
       <c r="U25">
-        <v>0.2408</v>
+        <v>0.2413</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>0.223</v>
+        <v>0.2463</v>
       </c>
       <c r="X25">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y25">
-        <v>1.0338</v>
+        <v>1.0284</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3153,22 +3192,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.66</v>
+        <v>6.85</v>
       </c>
       <c r="AE25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF25">
-        <v>0.258</v>
+        <v>0.268</v>
       </c>
       <c r="AG25">
-        <v>1.1123</v>
+        <v>1.0839</v>
       </c>
       <c r="AH25">
         <v>-0.21</v>
       </c>
       <c r="AM25">
-        <v>6.45</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3176,22 +3215,22 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26">
+        <v>5.5</v>
+      </c>
+      <c r="D26">
+        <v>-143</v>
+      </c>
+      <c r="E26">
+        <v>120</v>
+      </c>
+      <c r="F26" t="s">
         <v>85</v>
       </c>
-      <c r="C26">
-        <v>4.5</v>
-      </c>
-      <c r="D26">
-        <v>-106</v>
-      </c>
-      <c r="E26">
-        <v>-110</v>
-      </c>
-      <c r="F26" t="s">
-        <v>86</v>
-      </c>
       <c r="G26">
-        <v>823015</v>
+        <v>824555</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
@@ -3209,43 +3248,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2198</v>
+        <v>0.2651</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="P26">
-        <v>4.23</v>
+        <v>4.08</v>
       </c>
       <c r="Q26">
-        <v>0.1727</v>
+        <v>0.2456</v>
       </c>
       <c r="R26">
-        <v>0.355</v>
+        <v>0.363</v>
       </c>
       <c r="S26" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="T26">
-        <v>0.2606</v>
+        <v>0.2462</v>
       </c>
       <c r="U26">
-        <v>0.2015</v>
+        <v>0.2408</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>0.215</v>
+        <v>0.223</v>
       </c>
       <c r="X26">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y26">
-        <v>0.948</v>
+        <v>1.0338</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3254,22 +3293,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>5.32</v>
+        <v>6.61</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF26">
-        <v>0.2031</v>
+        <v>0.258</v>
       </c>
       <c r="AG26">
-        <v>1.1772</v>
+        <v>1.1036</v>
       </c>
       <c r="AH26">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AM26">
-        <v>5.52</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3283,13 +3322,13 @@
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>120</v>
+        <v>-106</v>
       </c>
       <c r="E27">
-        <v>-137</v>
+        <v>-110</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>823015</v>
@@ -3310,43 +3349,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1703</v>
+        <v>0.2198</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="P27">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="Q27">
-        <v>0.2019</v>
+        <v>0.1727</v>
       </c>
       <c r="R27">
-        <v>0.342</v>
+        <v>0.355</v>
       </c>
       <c r="S27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2659</v>
+        <v>0.2618</v>
       </c>
       <c r="U27">
-        <v>0.2405</v>
+        <v>0.1987</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2371</v>
+        <v>0.215</v>
       </c>
       <c r="X27">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y27">
-        <v>1.0358</v>
+        <v>0.9078</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3355,22 +3394,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>5.03</v>
+        <v>5.08</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1811</v>
+        <v>0.2031</v>
       </c>
       <c r="AG27">
-        <v>1.2011</v>
+        <v>1.1736</v>
       </c>
       <c r="AH27">
         <v>0.2</v>
       </c>
       <c r="AM27">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3378,34 +3417,76 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28">
         <v>4.5</v>
       </c>
       <c r="D28">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E28">
-        <v>-130</v>
+        <v>-137</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" t="s">
-        <v>44</v>
+        <v>88</v>
+      </c>
+      <c r="G28">
+        <v>823015</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I28">
+        <v>5.5</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
+      <c r="M28">
+        <v>0.1703</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28">
+        <v>104</v>
+      </c>
+      <c r="P28">
+        <v>4.06</v>
+      </c>
+      <c r="Q28">
+        <v>0.2019</v>
+      </c>
+      <c r="R28">
+        <v>0.342</v>
+      </c>
       <c r="S28" t="s">
-        <v>44</v>
-      </c>
-      <c r="V28" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T28">
+        <v>0.2751</v>
+      </c>
+      <c r="U28">
+        <v>0.2466</v>
+      </c>
+      <c r="V28">
+        <v>9</v>
+      </c>
+      <c r="W28">
+        <v>0.2371</v>
+      </c>
+      <c r="X28">
+        <v>0.2231</v>
+      </c>
+      <c r="Y28">
+        <v>1.0581</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3413,8 +3494,23 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
+      <c r="AD28">
+        <v>5.27</v>
+      </c>
       <c r="AE28" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF28">
+        <v>0.1811</v>
+      </c>
+      <c r="AG28">
+        <v>1.2331</v>
+      </c>
+      <c r="AH28">
+        <v>0.2</v>
+      </c>
+      <c r="AM28">
+        <v>5.47</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3434,7 +3530,7 @@
         <v>-120</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G29">
         <v>824963</v>
@@ -3473,7 +3569,7 @@
         <v>0.363</v>
       </c>
       <c r="S29" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="T29">
         <v>0.2504</v>
@@ -3488,7 +3584,7 @@
         <v>0.2479</v>
       </c>
       <c r="X29">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y29">
         <v>1.0327</v>
@@ -3500,22 +3596,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="AE29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF29">
         <v>0.2532</v>
       </c>
       <c r="AG29">
-        <v>1.1312</v>
+        <v>1.1224</v>
       </c>
       <c r="AH29">
         <v>-0.21</v>
       </c>
       <c r="AM29">
-        <v>6.49</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3523,19 +3619,19 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
         <v>91</v>
       </c>
-      <c r="F30" t="s">
-        <v>70</v>
-      </c>
       <c r="G30">
-        <v>822692</v>
+        <v>824963</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3547,43 +3643,43 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.1834</v>
+        <v>0.2126</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="P30">
-        <v>4.57</v>
+        <v>4.19</v>
       </c>
       <c r="Q30">
-        <v>0.1159</v>
+        <v>0.2066</v>
       </c>
       <c r="R30">
-        <v>0.257</v>
+        <v>0.377</v>
       </c>
       <c r="S30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2296</v>
+        <v>0.1826</v>
       </c>
       <c r="U30">
-        <v>0.2237</v>
+        <v>0.1803</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2196</v>
+        <v>0.2083</v>
       </c>
       <c r="X30">
-        <v>0.2214</v>
+        <v>0.2231</v>
       </c>
       <c r="Y30">
-        <v>1.0003</v>
+        <v>0.9268</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3592,22 +3688,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
       </c>
       <c r="AF30">
-        <v>0.1661</v>
+        <v>0.2104</v>
       </c>
       <c r="AG30">
-        <v>1.0373</v>
+        <v>0.8184</v>
       </c>
       <c r="AH30">
         <v>0.2</v>
       </c>
       <c r="AM30">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3615,67 +3711,34 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>130</v>
+      </c>
+      <c r="E31">
+        <v>-155</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31">
-        <v>822772</v>
+        <v>83</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
-      </c>
-      <c r="I31">
-        <v>3</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.2253</v>
-      </c>
-      <c r="N31">
         <v>4</v>
       </c>
-      <c r="O31">
-        <v>64</v>
-      </c>
-      <c r="P31">
-        <v>4.03</v>
-      </c>
-      <c r="Q31">
-        <v>0.1406</v>
-      </c>
-      <c r="R31">
-        <v>0.242</v>
-      </c>
       <c r="S31" t="s">
-        <v>49</v>
-      </c>
-      <c r="T31">
-        <v>0.1676</v>
-      </c>
-      <c r="U31">
-        <v>0.1841</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.2075</v>
-      </c>
-      <c r="X31">
-        <v>0.2214</v>
-      </c>
-      <c r="Y31">
-        <v>0.9491</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3683,23 +3746,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>1.78</v>
-      </c>
       <c r="AE31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF31">
-        <v>0.2048</v>
-      </c>
-      <c r="AG31">
-        <v>0.7573</v>
-      </c>
-      <c r="AH31">
-        <v>0.2</v>
-      </c>
-      <c r="AM31">
-        <v>1.98</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3709,65 +3757,32 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>125</v>
+      </c>
+      <c r="E32">
+        <v>-130</v>
+      </c>
       <c r="F32" t="s">
-        <v>89</v>
-      </c>
-      <c r="G32">
-        <v>824963</v>
+        <v>91</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
-        <v>5.4</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2126</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>121</v>
-      </c>
-      <c r="P32">
-        <v>4.19</v>
-      </c>
-      <c r="Q32">
-        <v>0.2066</v>
-      </c>
-      <c r="R32">
-        <v>0.377</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>49</v>
-      </c>
-      <c r="T32">
-        <v>0.1859</v>
-      </c>
-      <c r="U32">
-        <v>0.1836</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2083</v>
-      </c>
-      <c r="X32">
-        <v>0.2214</v>
-      </c>
-      <c r="Y32">
-        <v>0.9889</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3775,23 +3790,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>3.99</v>
-      </c>
       <c r="AE32" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF32">
-        <v>0.2104</v>
-      </c>
-      <c r="AG32">
-        <v>0.8397</v>
-      </c>
-      <c r="AH32">
-        <v>0.2</v>
-      </c>
-      <c r="AM32">
-        <v>4.19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3811,7 +3811,7 @@
         <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G33">
         <v>823180</v>
@@ -3850,7 +3850,7 @@
         <v>0.369</v>
       </c>
       <c r="S33" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="T33">
         <v>0.3543</v>
@@ -3880,7 +3880,7 @@
         <v>7.38</v>
       </c>
       <c r="AE33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AF33">
         <v>0.1965</v>

--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -187,6 +187,9 @@
     <t>Grayson Rodriguez</t>
   </si>
   <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
     <t>Bubba Chandler</t>
   </si>
   <si>
@@ -212,9 +215,6 @@
   </si>
   <si>
     <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
   </si>
   <si>
     <t>Tanner Gordon</t>
@@ -875,7 +875,7 @@
         <v>0.2236</v>
       </c>
       <c r="X2">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y2">
         <v>0.9046</v>
@@ -896,7 +896,7 @@
         <v>0.2033</v>
       </c>
       <c r="AG2">
-        <v>0.8563</v>
+        <v>0.8561</v>
       </c>
       <c r="AH2">
         <v>0.2</v>
@@ -976,7 +976,7 @@
         <v>0.187</v>
       </c>
       <c r="X3">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -997,7 +997,7 @@
         <v>0.1922</v>
       </c>
       <c r="AG3">
-        <v>0.6974</v>
+        <v>0.6972</v>
       </c>
       <c r="AH3">
         <v>0.2</v>
@@ -1032,7 +1032,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1044,22 +1044,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1896</v>
+        <v>0.1881</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="P4">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="Q4">
-        <v>0.1171</v>
+        <v>0.114</v>
       </c>
       <c r="R4">
-        <v>0.357</v>
+        <v>0.363</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1077,7 +1077,7 @@
         <v>0.1756</v>
       </c>
       <c r="X4">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y4">
         <v>0.88</v>
@@ -1089,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1637</v>
+        <v>0.1612</v>
       </c>
       <c r="AG4">
-        <v>0.8703</v>
+        <v>0.87</v>
       </c>
       <c r="AH4">
         <v>0.2</v>
       </c>
       <c r="AM4">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1145,22 +1145,22 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.176</v>
+        <v>0.1757</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P5">
         <v>4.09</v>
       </c>
       <c r="Q5">
-        <v>0.2294</v>
+        <v>0.2273</v>
       </c>
       <c r="R5">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1178,7 +1178,7 @@
         <v>0.2171</v>
       </c>
       <c r="X5">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y5">
         <v>0.8982</v>
@@ -1190,22 +1190,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1948</v>
+        <v>0.194</v>
       </c>
       <c r="AG5">
-        <v>0.9117</v>
+        <v>0.9115</v>
       </c>
       <c r="AH5">
         <v>0.2</v>
       </c>
       <c r="AM5">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1234,7 +1234,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1246,22 +1246,22 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.1725</v>
+        <v>0.1744</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P6">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="Q6">
-        <v>0.1529</v>
+        <v>0.1609</v>
       </c>
       <c r="R6">
-        <v>0.298</v>
+        <v>0.303</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1279,7 +1279,7 @@
         <v>0.2345</v>
       </c>
       <c r="X6">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y6">
         <v>0.9287</v>
@@ -1291,22 +1291,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.86</v>
+        <v>3.97</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1667</v>
+        <v>0.1703</v>
       </c>
       <c r="AG6">
-        <v>1.1663</v>
+        <v>1.166</v>
       </c>
       <c r="AH6">
         <v>0.2</v>
       </c>
       <c r="AM6">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>0.1955</v>
+        <v>0.1952</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -1380,7 +1380,7 @@
         <v>0.2555</v>
       </c>
       <c r="X7">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y7">
         <v>1.0648</v>
@@ -1398,10 +1398,10 @@
         <v>53</v>
       </c>
       <c r="AF7">
-        <v>0.2024</v>
+        <v>0.2022</v>
       </c>
       <c r="AG7">
-        <v>1.1676</v>
+        <v>1.1674</v>
       </c>
       <c r="AH7">
         <v>-0.21</v>
@@ -1481,7 +1481,7 @@
         <v>0.2535</v>
       </c>
       <c r="X8">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y8">
         <v>1.0973</v>
@@ -1502,7 +1502,7 @@
         <v>0.2736</v>
       </c>
       <c r="AG8">
-        <v>1.2188</v>
+        <v>1.2185</v>
       </c>
       <c r="AH8">
         <v>-0.91</v>
@@ -1534,10 +1534,10 @@
         <v>823988</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1549,22 +1549,22 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.2047</v>
+        <v>0.206</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="P9">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="Q9">
-        <v>0.2768</v>
+        <v>0.2796</v>
       </c>
       <c r="R9">
-        <v>0.359</v>
+        <v>0.317</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1582,7 +1582,7 @@
         <v>0.211</v>
       </c>
       <c r="X9">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y9">
         <v>0.88</v>
@@ -1594,22 +1594,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2306</v>
+        <v>0.2293</v>
       </c>
       <c r="AG9">
-        <v>0.7994</v>
+        <v>0.7992</v>
       </c>
       <c r="AH9">
         <v>0.2</v>
       </c>
       <c r="AM9">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1617,7 +1617,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1629,7 +1629,7 @@
         <v>-147</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>823255</v>
@@ -1683,7 +1683,7 @@
         <v>0.2163</v>
       </c>
       <c r="X10">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y10">
         <v>1.002</v>
@@ -1704,7 +1704,7 @@
         <v>0.2154</v>
       </c>
       <c r="AG10">
-        <v>0.8502</v>
+        <v>0.85</v>
       </c>
       <c r="AH10">
         <v>0.2</v>
@@ -1718,7 +1718,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1730,7 +1730,7 @@
         <v>-119</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>823255</v>
@@ -1739,7 +1739,7 @@
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1751,22 +1751,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.1486</v>
+        <v>0.1477</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="P11">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="Q11">
-        <v>0.0575</v>
+        <v>0.0676</v>
       </c>
       <c r="R11">
-        <v>0.303</v>
+        <v>0.27</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1784,7 +1784,7 @@
         <v>0.2374</v>
       </c>
       <c r="X11">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y11">
         <v>1.0872</v>
@@ -1796,22 +1796,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1263</v>
+        <v>0.1261</v>
       </c>
       <c r="AG11">
-        <v>1.2638</v>
+        <v>1.2635</v>
       </c>
       <c r="AH11">
         <v>0.2</v>
       </c>
       <c r="AM11">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1819,7 +1819,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>7.5</v>
@@ -1831,7 +1831,7 @@
         <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>823096</v>
@@ -1885,7 +1885,7 @@
         <v>0.2428</v>
       </c>
       <c r="X12">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y12">
         <v>0.926</v>
@@ -1906,7 +1906,7 @@
         <v>0.304</v>
       </c>
       <c r="AG12">
-        <v>1.319</v>
+        <v>1.3186</v>
       </c>
       <c r="AH12">
         <v>-0.91</v>
@@ -1920,7 +1920,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1932,7 +1932,7 @@
         <v>-153</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>823096</v>
@@ -1941,7 +1941,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1953,22 +1953,22 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2433</v>
+        <v>0.2429</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="P13">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q13">
-        <v>0.2478</v>
+        <v>0.2584</v>
       </c>
       <c r="R13">
-        <v>0.361</v>
+        <v>0.308</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1986,7 +1986,7 @@
         <v>0.2212</v>
       </c>
       <c r="X13">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y13">
         <v>0.9267</v>
@@ -1998,22 +1998,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2449</v>
+        <v>0.2477</v>
       </c>
       <c r="AG13">
-        <v>0.6886</v>
+        <v>0.6885</v>
       </c>
       <c r="AH13">
         <v>0.2</v>
       </c>
       <c r="AM13">
-        <v>3.87</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2021,7 +2021,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2033,7 +2033,7 @@
         <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>823825</v>
@@ -2087,7 +2087,7 @@
         <v>0.211</v>
       </c>
       <c r="X14">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y14">
         <v>0.9306</v>
@@ -2108,7 +2108,7 @@
         <v>0.222</v>
       </c>
       <c r="AG14">
-        <v>0.9511</v>
+        <v>0.9508</v>
       </c>
       <c r="AH14">
         <v>0.2</v>
@@ -2122,7 +2122,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>3.5</v>
@@ -2134,13 +2134,13 @@
         <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>823825</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -2188,7 +2188,7 @@
         <v>0.2141</v>
       </c>
       <c r="X15">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y15">
         <v>0.9774</v>
@@ -2200,7 +2200,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2209,13 +2209,13 @@
         <v>0.1974</v>
       </c>
       <c r="AG15">
-        <v>0.7349</v>
+        <v>0.7348</v>
       </c>
       <c r="AH15">
         <v>0.2</v>
       </c>
       <c r="AM15">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2277,10 +2277,10 @@
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2396</v>
+        <v>0.2413</v>
       </c>
       <c r="U16">
-        <v>0.2402</v>
+        <v>0.239</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2289,10 +2289,10 @@
         <v>0.2065</v>
       </c>
       <c r="X16">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y16">
-        <v>1.0387</v>
+        <v>1.0422</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2301,7 +2301,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2310,13 +2310,13 @@
         <v>0.1721</v>
       </c>
       <c r="AG16">
-        <v>1.074</v>
+        <v>1.0812</v>
       </c>
       <c r="AH16">
         <v>0.2</v>
       </c>
       <c r="AM16">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2381,7 +2381,7 @@
         <v>0.2196</v>
       </c>
       <c r="X17">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y17">
         <v>1.0263</v>
@@ -2402,7 +2402,7 @@
         <v>0.1661</v>
       </c>
       <c r="AG17">
-        <v>1.0962</v>
+        <v>1.0959</v>
       </c>
       <c r="AH17">
         <v>0.2</v>
@@ -2482,7 +2482,7 @@
         <v>0.2469</v>
       </c>
       <c r="X18">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y18">
         <v>0.9712</v>
@@ -2494,7 +2494,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="AE18" t="s">
         <v>53</v>
@@ -2503,13 +2503,13 @@
         <v>0.2332</v>
       </c>
       <c r="AG18">
-        <v>1.1439</v>
+        <v>1.1436</v>
       </c>
       <c r="AH18">
         <v>-0.21</v>
       </c>
       <c r="AM18">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2535,7 +2535,7 @@
         <v>823506</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I19">
         <v>4.3</v>
@@ -2583,7 +2583,7 @@
         <v>0.2188</v>
       </c>
       <c r="X19">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y19">
         <v>0.9926</v>
@@ -2604,7 +2604,7 @@
         <v>0.1205</v>
       </c>
       <c r="AG19">
-        <v>1.0129</v>
+        <v>1.0126</v>
       </c>
       <c r="AH19">
         <v>0.2</v>
@@ -2684,7 +2684,7 @@
         <v>0.1891</v>
       </c>
       <c r="X20">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y20">
         <v>0.9603</v>
@@ -2705,7 +2705,7 @@
         <v>0.1538</v>
       </c>
       <c r="AG20">
-        <v>0.7883</v>
+        <v>0.7881</v>
       </c>
       <c r="AH20">
         <v>0.2</v>
@@ -2776,7 +2776,7 @@
         <v>0.2075</v>
       </c>
       <c r="X21">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y21">
         <v>0.9489</v>
@@ -2788,7 +2788,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2797,13 +2797,13 @@
         <v>0.2048</v>
       </c>
       <c r="AG21">
-        <v>0.8146</v>
+        <v>0.8144</v>
       </c>
       <c r="AH21">
         <v>0.2</v>
       </c>
       <c r="AM21">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2877,7 +2877,7 @@
         <v>0.2234</v>
       </c>
       <c r="X22">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y22">
         <v>0.99</v>
@@ -2898,7 +2898,7 @@
         <v>0.2205</v>
       </c>
       <c r="AG22">
-        <v>1.0329</v>
+        <v>1.0326</v>
       </c>
       <c r="AH22">
         <v>0.2</v>
@@ -2930,7 +2930,7 @@
         <v>823584</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I23">
         <v>4.2</v>
@@ -2978,7 +2978,7 @@
         <v>0.2144</v>
       </c>
       <c r="X23">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y23">
         <v>0.9835</v>
@@ -2999,7 +2999,7 @@
         <v>0.2346</v>
       </c>
       <c r="AG23">
-        <v>1.0052</v>
+        <v>1.0049</v>
       </c>
       <c r="AH23">
         <v>0.2</v>
@@ -3079,7 +3079,7 @@
         <v>0.2201</v>
       </c>
       <c r="X24">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y24">
         <v>0.9998</v>
@@ -3100,7 +3100,7 @@
         <v>0.2359</v>
       </c>
       <c r="AG24">
-        <v>1.0526</v>
+        <v>1.0523</v>
       </c>
       <c r="AH24">
         <v>0.2</v>
@@ -3180,7 +3180,7 @@
         <v>0.2463</v>
       </c>
       <c r="X25">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y25">
         <v>1.0284</v>
@@ -3201,7 +3201,7 @@
         <v>0.268</v>
       </c>
       <c r="AG25">
-        <v>1.0839</v>
+        <v>1.0836</v>
       </c>
       <c r="AH25">
         <v>-0.21</v>
@@ -3281,7 +3281,7 @@
         <v>0.223</v>
       </c>
       <c r="X26">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y26">
         <v>1.0338</v>
@@ -3302,7 +3302,7 @@
         <v>0.258</v>
       </c>
       <c r="AG26">
-        <v>1.1036</v>
+        <v>1.1034</v>
       </c>
       <c r="AH26">
         <v>-0.21</v>
@@ -3382,7 +3382,7 @@
         <v>0.215</v>
       </c>
       <c r="X27">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y27">
         <v>0.9078</v>
@@ -3403,7 +3403,7 @@
         <v>0.2031</v>
       </c>
       <c r="AG27">
-        <v>1.1736</v>
+        <v>1.1733</v>
       </c>
       <c r="AH27">
         <v>0.2</v>
@@ -3483,7 +3483,7 @@
         <v>0.2371</v>
       </c>
       <c r="X28">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y28">
         <v>1.0581</v>
@@ -3504,7 +3504,7 @@
         <v>0.1811</v>
       </c>
       <c r="AG28">
-        <v>1.2331</v>
+        <v>1.2328</v>
       </c>
       <c r="AH28">
         <v>0.2</v>
@@ -3584,7 +3584,7 @@
         <v>0.2479</v>
       </c>
       <c r="X29">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y29">
         <v>1.0327</v>
@@ -3605,7 +3605,7 @@
         <v>0.2532</v>
       </c>
       <c r="AG29">
-        <v>1.1224</v>
+        <v>1.1221</v>
       </c>
       <c r="AH29">
         <v>-0.21</v>
@@ -3676,7 +3676,7 @@
         <v>0.2083</v>
       </c>
       <c r="X30">
-        <v>0.2231</v>
+        <v>0.2232</v>
       </c>
       <c r="Y30">
         <v>0.9268</v>
@@ -3697,7 +3697,7 @@
         <v>0.2104</v>
       </c>
       <c r="AG30">
-        <v>0.8184</v>
+        <v>0.8182</v>
       </c>
       <c r="AH30">
         <v>0.2</v>

--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -181,42 +181,42 @@
     <t>Cleveland Guardians @ Los Angeles Angels</t>
   </si>
   <si>
+    <t>Grayson Rodriguez</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vásquez</t>
+  </si>
+  <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Grayson Rodriguez</t>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
   </si>
   <si>
     <t>Limited starter</t>
   </si>
   <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Randy Vásquez</t>
-  </si>
-  <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
     <t>Tanner Gordon</t>
   </si>
   <si>
@@ -253,52 +253,52 @@
     <t>Milwaukee Brewers @ New York Mets</t>
   </si>
   <si>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
+    <t>AJ Smith-Shawver</t>
+  </si>
+  <si>
+    <t>JT Ginn</t>
+  </si>
+  <si>
+    <t>Landen Roupp</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
-  </si>
-  <si>
-    <t>AJ Smith-Shawver</t>
-  </si>
-  <si>
-    <t>JT Ginn</t>
-  </si>
-  <si>
-    <t>Landen Roupp</t>
   </si>
 </sst>
 </file>
@@ -875,7 +875,7 @@
         <v>0.2236</v>
       </c>
       <c r="X2">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y2">
         <v>0.9046</v>
@@ -887,7 +887,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -896,13 +896,13 @@
         <v>0.2033</v>
       </c>
       <c r="AG2">
-        <v>0.8561</v>
+        <v>0.8608</v>
       </c>
       <c r="AH2">
         <v>0.2</v>
       </c>
       <c r="AM2">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -976,7 +976,7 @@
         <v>0.187</v>
       </c>
       <c r="X3">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -988,7 +988,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -997,13 +997,13 @@
         <v>0.1922</v>
       </c>
       <c r="AG3">
-        <v>0.6972</v>
+        <v>0.7011</v>
       </c>
       <c r="AH3">
         <v>0.2</v>
       </c>
       <c r="AM3">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1032,7 +1032,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1044,22 +1044,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1881</v>
+        <v>0.1895</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="P4">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="Q4">
-        <v>0.114</v>
+        <v>0.126</v>
       </c>
       <c r="R4">
-        <v>0.363</v>
+        <v>0.388</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1074,10 +1074,10 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.1756</v>
+        <v>0.1766</v>
       </c>
       <c r="X4">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y4">
         <v>0.88</v>
@@ -1089,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1612</v>
+        <v>0.1648</v>
       </c>
       <c r="AG4">
-        <v>0.87</v>
+        <v>0.8748</v>
       </c>
       <c r="AH4">
         <v>0.2</v>
       </c>
       <c r="AM4">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1145,22 +1145,22 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.1757</v>
+        <v>0.18</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="P5">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="Q5">
-        <v>0.2273</v>
+        <v>0.2422</v>
       </c>
       <c r="R5">
-        <v>0.355</v>
+        <v>0.39</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1175,10 +1175,10 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2171</v>
+        <v>0.2195</v>
       </c>
       <c r="X5">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y5">
         <v>0.8982</v>
@@ -1190,22 +1190,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.194</v>
+        <v>0.2043</v>
       </c>
       <c r="AG5">
-        <v>0.9115</v>
+        <v>0.9165</v>
       </c>
       <c r="AH5">
         <v>0.2</v>
       </c>
       <c r="AM5">
-        <v>3.98</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1234,7 +1234,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1246,22 +1246,22 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.1744</v>
+        <v>0.1783</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="P6">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="Q6">
-        <v>0.1609</v>
+        <v>0.1765</v>
       </c>
       <c r="R6">
-        <v>0.303</v>
+        <v>0.338</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1279,7 +1279,7 @@
         <v>0.2345</v>
       </c>
       <c r="X6">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y6">
         <v>0.9287</v>
@@ -1291,22 +1291,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.97</v>
+        <v>4.34</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1703</v>
+        <v>0.1777</v>
       </c>
       <c r="AG6">
-        <v>1.166</v>
+        <v>1.1724</v>
       </c>
       <c r="AH6">
         <v>0.2</v>
       </c>
       <c r="AM6">
-        <v>4.17</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1335,7 +1335,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>0.1952</v>
+        <v>0.1957</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="P7">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="Q7">
-        <v>0.2165</v>
+        <v>0.2137</v>
       </c>
       <c r="R7">
-        <v>0.327</v>
+        <v>0.369</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1380,7 +1380,7 @@
         <v>0.2555</v>
       </c>
       <c r="X7">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y7">
         <v>1.0648</v>
@@ -1392,22 +1392,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.11</v>
+        <v>6.35</v>
       </c>
       <c r="AE7" t="s">
         <v>53</v>
       </c>
       <c r="AF7">
-        <v>0.2022</v>
+        <v>0.2023</v>
       </c>
       <c r="AG7">
-        <v>1.1674</v>
+        <v>1.1738</v>
       </c>
       <c r="AH7">
         <v>-0.21</v>
       </c>
       <c r="AM7">
-        <v>5.9</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1436,7 +1436,7 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1448,22 +1448,22 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.2553</v>
+        <v>0.2462</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="P8">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="Q8">
-        <v>0.3146</v>
+        <v>0.2165</v>
       </c>
       <c r="R8">
-        <v>0.308</v>
+        <v>0.327</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1481,7 +1481,7 @@
         <v>0.2535</v>
       </c>
       <c r="X8">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y8">
         <v>1.0973</v>
@@ -1493,22 +1493,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>7.64</v>
+        <v>6.69</v>
       </c>
       <c r="AE8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AF8">
-        <v>0.2736</v>
+        <v>0.2365</v>
       </c>
       <c r="AG8">
-        <v>1.2185</v>
+        <v>1.2253</v>
       </c>
       <c r="AH8">
-        <v>-0.91</v>
+        <v>-0.21</v>
       </c>
       <c r="AM8">
-        <v>6.73</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1516,7 +1516,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>4.5</v>
@@ -1534,10 +1534,10 @@
         <v>823988</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1549,22 +1549,22 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.206</v>
+        <v>0.2019</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="P9">
-        <v>4.54</v>
+        <v>4.49</v>
       </c>
       <c r="Q9">
-        <v>0.2796</v>
+        <v>0.2544</v>
       </c>
       <c r="R9">
-        <v>0.317</v>
+        <v>0.363</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1582,7 +1582,7 @@
         <v>0.211</v>
       </c>
       <c r="X9">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y9">
         <v>0.88</v>
@@ -1594,22 +1594,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2293</v>
+        <v>0.2209</v>
       </c>
       <c r="AG9">
-        <v>0.7992</v>
+        <v>0.8036</v>
       </c>
       <c r="AH9">
         <v>0.2</v>
       </c>
       <c r="AM9">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1617,7 +1617,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1629,7 +1629,7 @@
         <v>-147</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>823255</v>
@@ -1650,22 +1650,22 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2084</v>
+        <v>0.2056</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P10">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="Q10">
-        <v>0.2286</v>
+        <v>0.2264</v>
       </c>
       <c r="R10">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
@@ -1683,7 +1683,7 @@
         <v>0.2163</v>
       </c>
       <c r="X10">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y10">
         <v>1.002</v>
@@ -1695,22 +1695,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2154</v>
+        <v>0.2128</v>
       </c>
       <c r="AG10">
-        <v>0.85</v>
+        <v>0.8547</v>
       </c>
       <c r="AH10">
         <v>0.2</v>
       </c>
       <c r="AM10">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1718,7 +1718,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1730,7 +1730,7 @@
         <v>-119</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>823255</v>
@@ -1739,7 +1739,7 @@
         <v>42</v>
       </c>
       <c r="I11">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1751,22 +1751,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.1477</v>
+        <v>0.1473</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="P11">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="Q11">
-        <v>0.0676</v>
+        <v>0.0787</v>
       </c>
       <c r="R11">
-        <v>0.27</v>
+        <v>0.308</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1784,7 +1784,7 @@
         <v>0.2374</v>
       </c>
       <c r="X11">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y11">
         <v>1.0872</v>
@@ -1796,22 +1796,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1261</v>
+        <v>0.1262</v>
       </c>
       <c r="AG11">
-        <v>1.2635</v>
+        <v>1.2705</v>
       </c>
       <c r="AH11">
         <v>0.2</v>
       </c>
       <c r="AM11">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1819,7 +1819,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12">
         <v>7.5</v>
@@ -1831,7 +1831,7 @@
         <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>823096</v>
@@ -1852,22 +1852,22 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.3008</v>
+        <v>0.303</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P12">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="Q12">
-        <v>0.3088</v>
+        <v>0.3459</v>
       </c>
       <c r="R12">
-        <v>0.405</v>
+        <v>0.399</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
@@ -1885,7 +1885,7 @@
         <v>0.2428</v>
       </c>
       <c r="X12">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y12">
         <v>0.926</v>
@@ -1897,22 +1897,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>9.21</v>
+        <v>9.75</v>
       </c>
       <c r="AE12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AF12">
-        <v>0.304</v>
+        <v>0.3201</v>
       </c>
       <c r="AG12">
-        <v>1.3186</v>
+        <v>1.3259</v>
       </c>
       <c r="AH12">
         <v>-0.91</v>
       </c>
       <c r="AM12">
-        <v>8.3</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1920,7 +1920,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1932,7 +1932,7 @@
         <v>-153</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>823096</v>
@@ -1941,7 +1941,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1953,22 +1953,22 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2429</v>
+        <v>0.2444</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="P13">
         <v>4.08</v>
       </c>
       <c r="Q13">
-        <v>0.2584</v>
+        <v>0.2642</v>
       </c>
       <c r="R13">
-        <v>0.308</v>
+        <v>0.346</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1986,7 +1986,7 @@
         <v>0.2212</v>
       </c>
       <c r="X13">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y13">
         <v>0.9267</v>
@@ -1998,22 +1998,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2477</v>
+        <v>0.2512</v>
       </c>
       <c r="AG13">
-        <v>0.6885</v>
+        <v>0.6923</v>
       </c>
       <c r="AH13">
         <v>0.2</v>
       </c>
       <c r="AM13">
-        <v>3.77</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2021,7 +2021,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2033,7 +2033,7 @@
         <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>823825</v>
@@ -2087,7 +2087,7 @@
         <v>0.211</v>
       </c>
       <c r="X14">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y14">
         <v>0.9306</v>
@@ -2099,7 +2099,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2108,13 +2108,13 @@
         <v>0.222</v>
       </c>
       <c r="AG14">
-        <v>0.9508</v>
+        <v>0.9561</v>
       </c>
       <c r="AH14">
         <v>0.2</v>
       </c>
       <c r="AM14">
-        <v>4.81</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2122,7 +2122,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <v>3.5</v>
@@ -2134,13 +2134,13 @@
         <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>823825</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -2188,7 +2188,7 @@
         <v>0.2141</v>
       </c>
       <c r="X15">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y15">
         <v>0.9774</v>
@@ -2200,7 +2200,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2209,13 +2209,13 @@
         <v>0.1974</v>
       </c>
       <c r="AG15">
-        <v>0.7348</v>
+        <v>0.7388</v>
       </c>
       <c r="AH15">
         <v>0.2</v>
       </c>
       <c r="AM15">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
         <v>0.2065</v>
       </c>
       <c r="X16">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y16">
         <v>1.0422</v>
@@ -2301,7 +2301,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2310,13 +2310,13 @@
         <v>0.1721</v>
       </c>
       <c r="AG16">
-        <v>1.0812</v>
+        <v>1.0872</v>
       </c>
       <c r="AH16">
         <v>0.2</v>
       </c>
       <c r="AM16">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2381,7 +2381,7 @@
         <v>0.2196</v>
       </c>
       <c r="X17">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y17">
         <v>1.0263</v>
@@ -2393,7 +2393,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2402,13 +2402,13 @@
         <v>0.1661</v>
       </c>
       <c r="AG17">
-        <v>1.0959</v>
+        <v>1.102</v>
       </c>
       <c r="AH17">
         <v>0.2</v>
       </c>
       <c r="AM17">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2482,7 +2482,7 @@
         <v>0.2469</v>
       </c>
       <c r="X18">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y18">
         <v>0.9712</v>
@@ -2494,7 +2494,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.07</v>
+        <v>6.11</v>
       </c>
       <c r="AE18" t="s">
         <v>53</v>
@@ -2503,13 +2503,13 @@
         <v>0.2332</v>
       </c>
       <c r="AG18">
-        <v>1.1436</v>
+        <v>1.1499</v>
       </c>
       <c r="AH18">
         <v>-0.21</v>
       </c>
       <c r="AM18">
-        <v>5.86</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2535,7 +2535,7 @@
         <v>823506</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I19">
         <v>4.3</v>
@@ -2583,7 +2583,7 @@
         <v>0.2188</v>
       </c>
       <c r="X19">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y19">
         <v>0.9926</v>
@@ -2595,7 +2595,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2604,13 +2604,13 @@
         <v>0.1205</v>
       </c>
       <c r="AG19">
-        <v>1.0126</v>
+        <v>1.0182</v>
       </c>
       <c r="AH19">
         <v>0.2</v>
       </c>
       <c r="AM19">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2684,7 +2684,7 @@
         <v>0.1891</v>
       </c>
       <c r="X20">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y20">
         <v>0.9603</v>
@@ -2696,7 +2696,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2705,13 +2705,13 @@
         <v>0.1538</v>
       </c>
       <c r="AG20">
-        <v>0.7881</v>
+        <v>0.7925</v>
       </c>
       <c r="AH20">
         <v>0.2</v>
       </c>
       <c r="AM20">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2776,7 +2776,7 @@
         <v>0.2075</v>
       </c>
       <c r="X21">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y21">
         <v>0.9489</v>
@@ -2788,7 +2788,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2797,13 +2797,13 @@
         <v>0.2048</v>
       </c>
       <c r="AG21">
-        <v>0.8144</v>
+        <v>0.8189</v>
       </c>
       <c r="AH21">
         <v>0.2</v>
       </c>
       <c r="AM21">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2862,25 +2862,25 @@
         <v>0.353</v>
       </c>
       <c r="S22" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2304</v>
+        <v>0.2371</v>
       </c>
       <c r="U22">
-        <v>0.2222</v>
+        <v>0.229</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>0.2234</v>
       </c>
       <c r="X22">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y22">
-        <v>0.99</v>
+        <v>0.9909</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2889,7 +2889,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.91</v>
+        <v>5.09</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2898,13 +2898,13 @@
         <v>0.2205</v>
       </c>
       <c r="AG22">
-        <v>1.0326</v>
+        <v>1.0685</v>
       </c>
       <c r="AH22">
         <v>0.2</v>
       </c>
       <c r="AM22">
-        <v>5.11</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2912,7 +2912,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>4.5</v>
@@ -2930,7 +2930,7 @@
         <v>823584</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I23">
         <v>4.2</v>
@@ -2978,7 +2978,7 @@
         <v>0.2144</v>
       </c>
       <c r="X23">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y23">
         <v>0.9835</v>
@@ -2990,7 +2990,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2999,13 +2999,13 @@
         <v>0.2346</v>
       </c>
       <c r="AG23">
-        <v>1.0049</v>
+        <v>1.0104</v>
       </c>
       <c r="AH23">
         <v>0.2</v>
       </c>
       <c r="AM23">
-        <v>4.84</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3013,7 +3013,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -3025,7 +3025,7 @@
         <v>128</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24">
         <v>824878</v>
@@ -3079,7 +3079,7 @@
         <v>0.2201</v>
       </c>
       <c r="X24">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y24">
         <v>0.9998</v>
@@ -3091,7 +3091,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3100,13 +3100,13 @@
         <v>0.2359</v>
       </c>
       <c r="AG24">
-        <v>1.0523</v>
+        <v>1.0581</v>
       </c>
       <c r="AH24">
         <v>0.2</v>
       </c>
       <c r="AM24">
-        <v>5.76</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3114,7 +3114,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25">
         <v>6.5</v>
@@ -3126,7 +3126,7 @@
         <v>-143</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G25">
         <v>824555</v>
@@ -3180,7 +3180,7 @@
         <v>0.2463</v>
       </c>
       <c r="X25">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y25">
         <v>1.0284</v>
@@ -3192,7 +3192,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.85</v>
+        <v>6.88</v>
       </c>
       <c r="AE25" t="s">
         <v>53</v>
@@ -3201,13 +3201,13 @@
         <v>0.268</v>
       </c>
       <c r="AG25">
-        <v>1.0836</v>
+        <v>1.0896</v>
       </c>
       <c r="AH25">
         <v>-0.21</v>
       </c>
       <c r="AM25">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3215,7 +3215,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -3227,7 +3227,7 @@
         <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26">
         <v>824555</v>
@@ -3266,25 +3266,25 @@
         <v>0.363</v>
       </c>
       <c r="S26" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2462</v>
+        <v>0.2301</v>
       </c>
       <c r="U26">
-        <v>0.2408</v>
+        <v>0.2326</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>0.223</v>
       </c>
       <c r="X26">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y26">
-        <v>1.0338</v>
+        <v>1.0558</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3293,7 +3293,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>6.61</v>
+        <v>6.34</v>
       </c>
       <c r="AE26" t="s">
         <v>53</v>
@@ -3302,13 +3302,13 @@
         <v>0.258</v>
       </c>
       <c r="AG26">
-        <v>1.1034</v>
+        <v>1.0366</v>
       </c>
       <c r="AH26">
         <v>-0.21</v>
       </c>
       <c r="AM26">
-        <v>6.4</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3328,7 +3328,7 @@
         <v>-110</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G27">
         <v>823015</v>
@@ -3382,7 +3382,7 @@
         <v>0.215</v>
       </c>
       <c r="X27">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y27">
         <v>0.9078</v>
@@ -3394,7 +3394,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>5.08</v>
+        <v>5.11</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3403,13 +3403,13 @@
         <v>0.2031</v>
       </c>
       <c r="AG27">
-        <v>1.1733</v>
+        <v>1.1798</v>
       </c>
       <c r="AH27">
         <v>0.2</v>
       </c>
       <c r="AM27">
-        <v>5.28</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3417,7 +3417,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3429,7 +3429,7 @@
         <v>-137</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28">
         <v>823015</v>
@@ -3483,7 +3483,7 @@
         <v>0.2371</v>
       </c>
       <c r="X28">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y28">
         <v>1.0581</v>
@@ -3495,7 +3495,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.27</v>
+        <v>5.3</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3504,13 +3504,13 @@
         <v>0.1811</v>
       </c>
       <c r="AG28">
-        <v>1.2328</v>
+        <v>1.2396</v>
       </c>
       <c r="AH28">
         <v>0.2</v>
       </c>
       <c r="AM28">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3518,7 +3518,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29">
         <v>5.5</v>
@@ -3530,7 +3530,7 @@
         <v>-120</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G29">
         <v>824963</v>
@@ -3569,13 +3569,13 @@
         <v>0.363</v>
       </c>
       <c r="S29" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2504</v>
+        <v>0.2232</v>
       </c>
       <c r="U29">
-        <v>0.2308</v>
+        <v>0.2231</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -3584,10 +3584,10 @@
         <v>0.2479</v>
       </c>
       <c r="X29">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y29">
-        <v>1.0327</v>
+        <v>1.067</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3596,7 +3596,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>6.65</v>
+        <v>6.16</v>
       </c>
       <c r="AE29" t="s">
         <v>53</v>
@@ -3605,13 +3605,13 @@
         <v>0.2532</v>
       </c>
       <c r="AG29">
-        <v>1.1221</v>
+        <v>1.0057</v>
       </c>
       <c r="AH29">
         <v>-0.21</v>
       </c>
       <c r="AM29">
-        <v>6.44</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3619,10 +3619,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G30">
         <v>824963</v>
@@ -3676,7 +3676,7 @@
         <v>0.2083</v>
       </c>
       <c r="X30">
-        <v>0.2232</v>
+        <v>0.2219</v>
       </c>
       <c r="Y30">
         <v>0.9268</v>
@@ -3688,7 +3688,7 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
@@ -3697,13 +3697,13 @@
         <v>0.2104</v>
       </c>
       <c r="AG30">
-        <v>0.8182</v>
+        <v>0.8227</v>
       </c>
       <c r="AH30">
         <v>0.2</v>
       </c>
       <c r="AM30">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3711,7 +3711,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3723,7 +3723,7 @@
         <v>-155</v>
       </c>
       <c r="F31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>
@@ -3755,7 +3755,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>4.5</v>
@@ -3767,7 +3767,7 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>
@@ -3799,7 +3799,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33">
         <v>5.5</v>
@@ -3850,7 +3850,7 @@
         <v>0.369</v>
       </c>
       <c r="S33" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="T33">
         <v>0.3543</v>
@@ -3880,7 +3880,7 @@
         <v>7.38</v>
       </c>
       <c r="AE33" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AF33">
         <v>0.1965</v>

--- a/data/k-props/2026-08-26.xlsx
+++ b/data/k-props/2026-08-26.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="100">
   <si>
     <t>date</t>
   </si>
@@ -145,6 +145,9 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>Troy Melton</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>Matthew Boyd</t>
   </si>
   <si>
@@ -184,6 +190,9 @@
     <t>Grayson Rodriguez</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>Bubba Chandler</t>
   </si>
   <si>
@@ -233,6 +242,9 @@
   </si>
   <si>
     <t>Elmer Rodríguez</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Randy Dobnak</t>
@@ -880,17 +892,23 @@
       <c r="Y2">
         <v>0.9046</v>
       </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>-0.66</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>3.64</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.2033</v>
@@ -900,6 +918,18 @@
       </c>
       <c r="AH2">
         <v>0.2</v>
+      </c>
+      <c r="AI2">
+        <v>0.36</v>
+      </c>
+      <c r="AJ2">
+        <v>0.36</v>
+      </c>
+      <c r="AK2">
+        <v>0.16</v>
+      </c>
+      <c r="AL2">
+        <v>0.16</v>
       </c>
       <c r="AM2">
         <v>3.84</v>
@@ -910,7 +940,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>3.5</v>
@@ -981,17 +1011,23 @@
       <c r="Y3">
         <v>0.88</v>
       </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>-0.47</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3">
         <v>2.83</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.1922</v>
@@ -1001,6 +1037,18 @@
       </c>
       <c r="AH3">
         <v>0.2</v>
+      </c>
+      <c r="AI3">
+        <v>1.17</v>
+      </c>
+      <c r="AJ3">
+        <v>1.17</v>
+      </c>
+      <c r="AK3">
+        <v>0.97</v>
+      </c>
+      <c r="AL3">
+        <v>0.97</v>
       </c>
       <c r="AM3">
         <v>3.03</v>
@@ -1011,7 +1059,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -1023,7 +1071,7 @@
         <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>825039</v>
@@ -1082,17 +1130,23 @@
       <c r="Y4">
         <v>0.88</v>
       </c>
+      <c r="Z4">
+        <v>5</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB4">
+        <v>-0.31</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD4">
         <v>2.99</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.1648</v>
@@ -1102,6 +1156,18 @@
       </c>
       <c r="AH4">
         <v>0.2</v>
+      </c>
+      <c r="AI4">
+        <v>2.01</v>
+      </c>
+      <c r="AJ4">
+        <v>2.01</v>
+      </c>
+      <c r="AK4">
+        <v>1.81</v>
+      </c>
+      <c r="AL4">
+        <v>1.81</v>
       </c>
       <c r="AM4">
         <v>3.19</v>
@@ -1112,7 +1178,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1124,7 +1190,7 @@
         <v>-155</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>825039</v>
@@ -1183,17 +1249,23 @@
       <c r="Y5">
         <v>0.8982</v>
       </c>
+      <c r="Z5">
+        <v>9</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB5">
+        <v>-0.18</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD5">
         <v>4.12</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.2043</v>
@@ -1203,6 +1275,18 @@
       </c>
       <c r="AH5">
         <v>0.2</v>
+      </c>
+      <c r="AI5">
+        <v>4.88</v>
+      </c>
+      <c r="AJ5">
+        <v>4.88</v>
+      </c>
+      <c r="AK5">
+        <v>4.68</v>
+      </c>
+      <c r="AL5">
+        <v>4.68</v>
       </c>
       <c r="AM5">
         <v>4.32</v>
@@ -1213,7 +1297,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1225,7 +1309,7 @@
         <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>823180</v>
@@ -1284,17 +1368,23 @@
       <c r="Y6">
         <v>0.9287</v>
       </c>
+      <c r="Z6">
+        <v>5</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB6">
+        <v>0.04</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>4.34</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.1777</v>
@@ -1304,6 +1394,18 @@
       </c>
       <c r="AH6">
         <v>0.2</v>
+      </c>
+      <c r="AI6">
+        <v>0.66</v>
+      </c>
+      <c r="AJ6">
+        <v>0.66</v>
+      </c>
+      <c r="AK6">
+        <v>0.46</v>
+      </c>
+      <c r="AL6">
+        <v>0.46</v>
       </c>
       <c r="AM6">
         <v>4.54</v>
@@ -1314,7 +1416,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1326,7 +1428,7 @@
         <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>823180</v>
@@ -1385,17 +1487,23 @@
       <c r="Y7">
         <v>1.0648</v>
       </c>
+      <c r="Z7">
+        <v>6</v>
+      </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB7">
+        <v>0.64</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD7">
         <v>6.35</v>
       </c>
       <c r="AE7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AF7">
         <v>0.2023</v>
@@ -1405,6 +1513,18 @@
       </c>
       <c r="AH7">
         <v>-0.21</v>
+      </c>
+      <c r="AI7">
+        <v>-0.35</v>
+      </c>
+      <c r="AJ7">
+        <v>0.35</v>
+      </c>
+      <c r="AK7">
+        <v>-0.14</v>
+      </c>
+      <c r="AL7">
+        <v>0.14</v>
       </c>
       <c r="AM7">
         <v>6.14</v>
@@ -1415,7 +1535,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>6.5</v>
@@ -1427,7 +1547,7 @@
         <v>110</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>823988</v>
@@ -1486,17 +1606,23 @@
       <c r="Y8">
         <v>1.0973</v>
       </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
       <c r="AA8" t="s">
         <v>44</v>
       </c>
+      <c r="AB8">
+        <v>-0.02</v>
+      </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>6.69</v>
       </c>
       <c r="AE8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AF8">
         <v>0.2365</v>
@@ -1506,6 +1632,18 @@
       </c>
       <c r="AH8">
         <v>-0.21</v>
+      </c>
+      <c r="AI8">
+        <v>-5.69</v>
+      </c>
+      <c r="AJ8">
+        <v>5.69</v>
+      </c>
+      <c r="AK8">
+        <v>-5.48</v>
+      </c>
+      <c r="AL8">
+        <v>5.48</v>
       </c>
       <c r="AM8">
         <v>6.48</v>
@@ -1516,7 +1654,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>4.5</v>
@@ -1528,7 +1666,7 @@
         <v>-156</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>823988</v>
@@ -1587,17 +1725,23 @@
       <c r="Y9">
         <v>0.88</v>
       </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
       <c r="AA9" t="s">
         <v>44</v>
       </c>
+      <c r="AB9">
+        <v>-0.95</v>
+      </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AD9">
         <v>3.35</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.2209</v>
@@ -1607,6 +1751,18 @@
       </c>
       <c r="AH9">
         <v>0.2</v>
+      </c>
+      <c r="AI9">
+        <v>0.65</v>
+      </c>
+      <c r="AJ9">
+        <v>0.65</v>
+      </c>
+      <c r="AK9">
+        <v>0.45</v>
+      </c>
+      <c r="AL9">
+        <v>0.45</v>
       </c>
       <c r="AM9">
         <v>3.55</v>
@@ -1617,7 +1773,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1629,7 +1785,7 @@
         <v>-147</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>823255</v>
@@ -1688,17 +1844,23 @@
       <c r="Y10">
         <v>1.002</v>
       </c>
+      <c r="Z10">
+        <v>3</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>-0.32</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD10">
         <v>3.98</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.2128</v>
@@ -1708,6 +1870,18 @@
       </c>
       <c r="AH10">
         <v>0.2</v>
+      </c>
+      <c r="AI10">
+        <v>-0.98</v>
+      </c>
+      <c r="AJ10">
+        <v>0.98</v>
+      </c>
+      <c r="AK10">
+        <v>-1.18</v>
+      </c>
+      <c r="AL10">
+        <v>1.18</v>
       </c>
       <c r="AM10">
         <v>4.18</v>
@@ -1718,7 +1892,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1730,7 +1904,7 @@
         <v>-119</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>823255</v>
@@ -1789,17 +1963,23 @@
       <c r="Y11">
         <v>1.0872</v>
       </c>
+      <c r="Z11">
+        <v>2</v>
+      </c>
       <c r="AA11" t="s">
         <v>44</v>
       </c>
+      <c r="AB11">
+        <v>0.4</v>
+      </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD11">
         <v>3.7</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.1262</v>
@@ -1809,6 +1989,18 @@
       </c>
       <c r="AH11">
         <v>0.2</v>
+      </c>
+      <c r="AI11">
+        <v>-1.7</v>
+      </c>
+      <c r="AJ11">
+        <v>1.7</v>
+      </c>
+      <c r="AK11">
+        <v>-1.9</v>
+      </c>
+      <c r="AL11">
+        <v>1.9</v>
       </c>
       <c r="AM11">
         <v>3.9</v>
@@ -1819,7 +2011,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>7.5</v>
@@ -1831,7 +2023,7 @@
         <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>823096</v>
@@ -1890,17 +2082,23 @@
       <c r="Y12">
         <v>0.926</v>
       </c>
+      <c r="Z12">
+        <v>9</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB12">
+        <v>1.34</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AD12">
         <v>9.75</v>
       </c>
       <c r="AE12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AF12">
         <v>0.3201</v>
@@ -1910,6 +2108,18 @@
       </c>
       <c r="AH12">
         <v>-0.91</v>
+      </c>
+      <c r="AI12">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ12">
+        <v>0.75</v>
+      </c>
+      <c r="AK12">
+        <v>0.16</v>
+      </c>
+      <c r="AL12">
+        <v>0.16</v>
       </c>
       <c r="AM12">
         <v>8.84</v>
@@ -1920,7 +2130,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1932,7 +2142,7 @@
         <v>-153</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>823096</v>
@@ -1991,17 +2201,23 @@
       <c r="Y13">
         <v>0.9267</v>
       </c>
+      <c r="Z13">
+        <v>5</v>
+      </c>
       <c r="AA13" t="s">
         <v>44</v>
       </c>
+      <c r="AB13">
+        <v>-1.55</v>
+      </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AD13">
         <v>3.75</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.2512</v>
@@ -2011,6 +2227,18 @@
       </c>
       <c r="AH13">
         <v>0.2</v>
+      </c>
+      <c r="AI13">
+        <v>1.25</v>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
+        <v>1.05</v>
+      </c>
+      <c r="AL13">
+        <v>1.05</v>
       </c>
       <c r="AM13">
         <v>3.95</v>
@@ -2021,7 +2249,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2033,7 +2261,7 @@
         <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>823825</v>
@@ -2092,17 +2320,23 @@
       <c r="Y14">
         <v>0.9306</v>
       </c>
+      <c r="Z14">
+        <v>5</v>
+      </c>
       <c r="AA14" t="s">
         <v>44</v>
       </c>
+      <c r="AB14">
+        <v>-0.67</v>
+      </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD14">
         <v>4.63</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.222</v>
@@ -2112,6 +2346,18 @@
       </c>
       <c r="AH14">
         <v>0.2</v>
+      </c>
+      <c r="AI14">
+        <v>0.37</v>
+      </c>
+      <c r="AJ14">
+        <v>0.37</v>
+      </c>
+      <c r="AK14">
+        <v>0.17</v>
+      </c>
+      <c r="AL14">
+        <v>0.17</v>
       </c>
       <c r="AM14">
         <v>4.83</v>
@@ -2122,7 +2368,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>3.5</v>
@@ -2134,13 +2380,13 @@
         <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>823825</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -2193,17 +2439,23 @@
       <c r="Y15">
         <v>0.9774</v>
       </c>
+      <c r="Z15">
+        <v>2</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>-0.76</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AD15">
         <v>2.54</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.1974</v>
@@ -2213,6 +2465,18 @@
       </c>
       <c r="AH15">
         <v>0.2</v>
+      </c>
+      <c r="AI15">
+        <v>-0.54</v>
+      </c>
+      <c r="AJ15">
+        <v>0.54</v>
+      </c>
+      <c r="AK15">
+        <v>-0.74</v>
+      </c>
+      <c r="AL15">
+        <v>0.74</v>
       </c>
       <c r="AM15">
         <v>2.74</v>
@@ -2223,7 +2487,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2235,7 +2499,7 @@
         <v>-103</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>822692</v>
@@ -2294,17 +2558,23 @@
       <c r="Y16">
         <v>1.0422</v>
       </c>
+      <c r="Z16">
+        <v>5</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB16">
+        <v>0.76</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AD16">
         <v>4.06</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1721</v>
@@ -2314,6 +2584,18 @@
       </c>
       <c r="AH16">
         <v>0.2</v>
+      </c>
+      <c r="AI16">
+        <v>0.94</v>
+      </c>
+      <c r="AJ16">
+        <v>0.94</v>
+      </c>
+      <c r="AK16">
+        <v>0.74</v>
+      </c>
+      <c r="AL16">
+        <v>0.74</v>
       </c>
       <c r="AM16">
         <v>4.26</v>
@@ -2324,10 +2606,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G17">
         <v>822692</v>
@@ -2387,16 +2669,16 @@
         <v>1.0263</v>
       </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD17">
         <v>3.91</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1661</v>
@@ -2416,7 +2698,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>5.5</v>
@@ -2428,7 +2710,7 @@
         <v>-142</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>823506</v>
@@ -2487,17 +2769,23 @@
       <c r="Y18">
         <v>0.9712</v>
       </c>
+      <c r="Z18">
+        <v>5</v>
+      </c>
       <c r="AA18" t="s">
         <v>44</v>
       </c>
+      <c r="AB18">
+        <v>0.4</v>
+      </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD18">
         <v>6.11</v>
       </c>
       <c r="AE18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AF18">
         <v>0.2332</v>
@@ -2507,6 +2795,18 @@
       </c>
       <c r="AH18">
         <v>-0.21</v>
+      </c>
+      <c r="AI18">
+        <v>-1.11</v>
+      </c>
+      <c r="AJ18">
+        <v>1.11</v>
+      </c>
+      <c r="AK18">
+        <v>-0.9</v>
+      </c>
+      <c r="AL18">
+        <v>0.9</v>
       </c>
       <c r="AM18">
         <v>5.9</v>
@@ -2517,7 +2817,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C19">
         <v>3.5</v>
@@ -2529,13 +2829,13 @@
         <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>823506</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I19">
         <v>4.3</v>
@@ -2588,17 +2888,23 @@
       <c r="Y19">
         <v>0.9926</v>
       </c>
+      <c r="Z19">
+        <v>6</v>
+      </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB19">
+        <v>-0.82</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AD19">
         <v>2.48</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.1205</v>
@@ -2608,6 +2914,18 @@
       </c>
       <c r="AH19">
         <v>0.2</v>
+      </c>
+      <c r="AI19">
+        <v>3.52</v>
+      </c>
+      <c r="AJ19">
+        <v>3.52</v>
+      </c>
+      <c r="AK19">
+        <v>3.32</v>
+      </c>
+      <c r="AL19">
+        <v>3.32</v>
       </c>
       <c r="AM19">
         <v>2.68</v>
@@ -2618,7 +2936,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C20">
         <v>2.5</v>
@@ -2630,7 +2948,7 @@
         <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G20">
         <v>822772</v>
@@ -2689,17 +3007,23 @@
       <c r="Y20">
         <v>0.9603</v>
       </c>
+      <c r="Z20">
+        <v>5</v>
+      </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB20">
+        <v>0.28</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD20">
         <v>2.58</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.1538</v>
@@ -2709,6 +3033,18 @@
       </c>
       <c r="AH20">
         <v>0.2</v>
+      </c>
+      <c r="AI20">
+        <v>2.42</v>
+      </c>
+      <c r="AJ20">
+        <v>2.42</v>
+      </c>
+      <c r="AK20">
+        <v>2.22</v>
+      </c>
+      <c r="AL20">
+        <v>2.22</v>
       </c>
       <c r="AM20">
         <v>2.78</v>
@@ -2719,16 +3055,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G21">
         <v>822772</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I21">
         <v>3</v>
@@ -2782,16 +3118,16 @@
         <v>0.9489</v>
       </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD21">
         <v>1.93</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.2048</v>
@@ -2811,7 +3147,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>4.5</v>
@@ -2823,7 +3159,7 @@
         <v>100</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>823584</v>
@@ -2882,17 +3218,23 @@
       <c r="Y22">
         <v>0.9909</v>
       </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
       <c r="AA22" t="s">
         <v>44</v>
       </c>
+      <c r="AB22">
+        <v>0.79</v>
+      </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AD22">
         <v>5.09</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2205</v>
@@ -2902,6 +3244,18 @@
       </c>
       <c r="AH22">
         <v>0.2</v>
+      </c>
+      <c r="AI22">
+        <v>-5.09</v>
+      </c>
+      <c r="AJ22">
+        <v>5.09</v>
+      </c>
+      <c r="AK22">
+        <v>-5.29</v>
+      </c>
+      <c r="AL22">
+        <v>5.29</v>
       </c>
       <c r="AM22">
         <v>5.29</v>
@@ -2912,7 +3266,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>4.5</v>
@@ -2924,13 +3278,13 @@
         <v>-129</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>823584</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I23">
         <v>4.2</v>
@@ -2983,17 +3337,23 @@
       <c r="Y23">
         <v>0.9835</v>
       </c>
+      <c r="Z23">
+        <v>2</v>
+      </c>
       <c r="AA23" t="s">
         <v>44</v>
       </c>
+      <c r="AB23">
+        <v>0.36</v>
+      </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>4.66</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.2346</v>
@@ -3003,6 +3363,18 @@
       </c>
       <c r="AH23">
         <v>0.2</v>
+      </c>
+      <c r="AI23">
+        <v>-2.66</v>
+      </c>
+      <c r="AJ23">
+        <v>2.66</v>
+      </c>
+      <c r="AK23">
+        <v>-2.86</v>
+      </c>
+      <c r="AL23">
+        <v>2.86</v>
       </c>
       <c r="AM23">
         <v>4.86</v>
@@ -3013,7 +3385,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -3025,7 +3397,7 @@
         <v>128</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>824878</v>
@@ -3084,17 +3456,23 @@
       <c r="Y24">
         <v>0.9998</v>
       </c>
+      <c r="Z24">
+        <v>3</v>
+      </c>
       <c r="AA24" t="s">
         <v>44</v>
       </c>
+      <c r="AB24">
+        <v>1.29</v>
+      </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AD24">
         <v>5.59</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.2359</v>
@@ -3104,6 +3482,18 @@
       </c>
       <c r="AH24">
         <v>0.2</v>
+      </c>
+      <c r="AI24">
+        <v>-2.59</v>
+      </c>
+      <c r="AJ24">
+        <v>2.59</v>
+      </c>
+      <c r="AK24">
+        <v>-2.79</v>
+      </c>
+      <c r="AL24">
+        <v>2.79</v>
       </c>
       <c r="AM24">
         <v>5.79</v>
@@ -3114,7 +3504,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>6.5</v>
@@ -3126,7 +3516,7 @@
         <v>-143</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G25">
         <v>824555</v>
@@ -3185,17 +3575,23 @@
       <c r="Y25">
         <v>1.0284</v>
       </c>
+      <c r="Z25">
+        <v>4</v>
+      </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>0.17</v>
+      </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD25">
         <v>6.88</v>
       </c>
       <c r="AE25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AF25">
         <v>0.268</v>
@@ -3205,6 +3601,18 @@
       </c>
       <c r="AH25">
         <v>-0.21</v>
+      </c>
+      <c r="AI25">
+        <v>-2.88</v>
+      </c>
+      <c r="AJ25">
+        <v>2.88</v>
+      </c>
+      <c r="AK25">
+        <v>-2.67</v>
+      </c>
+      <c r="AL25">
+        <v>2.67</v>
       </c>
       <c r="AM25">
         <v>6.67</v>
@@ -3215,7 +3623,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -3227,7 +3635,7 @@
         <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G26">
         <v>824555</v>
@@ -3286,17 +3694,23 @@
       <c r="Y26">
         <v>1.0558</v>
       </c>
+      <c r="Z26">
+        <v>3</v>
+      </c>
       <c r="AA26" t="s">
         <v>44</v>
       </c>
+      <c r="AB26">
+        <v>0.63</v>
+      </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD26">
         <v>6.34</v>
       </c>
       <c r="AE26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AF26">
         <v>0.258</v>
@@ -3306,6 +3720,18 @@
       </c>
       <c r="AH26">
         <v>-0.21</v>
+      </c>
+      <c r="AI26">
+        <v>-3.34</v>
+      </c>
+      <c r="AJ26">
+        <v>3.34</v>
+      </c>
+      <c r="AK26">
+        <v>-3.13</v>
+      </c>
+      <c r="AL26">
+        <v>3.13</v>
       </c>
       <c r="AM26">
         <v>6.13</v>
@@ -3316,7 +3742,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3328,7 +3754,7 @@
         <v>-110</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G27">
         <v>823015</v>
@@ -3387,17 +3813,23 @@
       <c r="Y27">
         <v>0.9078</v>
       </c>
+      <c r="Z27">
+        <v>4</v>
+      </c>
       <c r="AA27" t="s">
         <v>44</v>
       </c>
+      <c r="AB27">
+        <v>0.81</v>
+      </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AD27">
         <v>5.11</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>0.2031</v>
@@ -3407,6 +3839,18 @@
       </c>
       <c r="AH27">
         <v>0.2</v>
+      </c>
+      <c r="AI27">
+        <v>-1.11</v>
+      </c>
+      <c r="AJ27">
+        <v>1.11</v>
+      </c>
+      <c r="AK27">
+        <v>-1.31</v>
+      </c>
+      <c r="AL27">
+        <v>1.31</v>
       </c>
       <c r="AM27">
         <v>5.31</v>
@@ -3417,7 +3861,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3429,7 +3873,7 @@
         <v>-137</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G28">
         <v>823015</v>
@@ -3488,17 +3932,23 @@
       <c r="Y28">
         <v>1.0581</v>
       </c>
+      <c r="Z28">
+        <v>3</v>
+      </c>
       <c r="AA28" t="s">
         <v>44</v>
       </c>
+      <c r="AB28">
+        <v>1</v>
+      </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="AD28">
         <v>5.3</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF28">
         <v>0.1811</v>
@@ -3508,6 +3958,18 @@
       </c>
       <c r="AH28">
         <v>0.2</v>
+      </c>
+      <c r="AI28">
+        <v>-2.3</v>
+      </c>
+      <c r="AJ28">
+        <v>2.3</v>
+      </c>
+      <c r="AK28">
+        <v>-2.5</v>
+      </c>
+      <c r="AL28">
+        <v>2.5</v>
       </c>
       <c r="AM28">
         <v>5.5</v>
@@ -3518,7 +3980,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>5.5</v>
@@ -3530,7 +3992,7 @@
         <v>-120</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G29">
         <v>824963</v>
@@ -3589,17 +4051,23 @@
       <c r="Y29">
         <v>1.067</v>
       </c>
+      <c r="Z29">
+        <v>5</v>
+      </c>
       <c r="AA29" t="s">
         <v>44</v>
       </c>
+      <c r="AB29">
+        <v>0.45</v>
+      </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD29">
         <v>6.16</v>
       </c>
       <c r="AE29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AF29">
         <v>0.2532</v>
@@ -3609,6 +4077,18 @@
       </c>
       <c r="AH29">
         <v>-0.21</v>
+      </c>
+      <c r="AI29">
+        <v>-1.16</v>
+      </c>
+      <c r="AJ29">
+        <v>1.16</v>
+      </c>
+      <c r="AK29">
+        <v>-0.95</v>
+      </c>
+      <c r="AL29">
+        <v>0.95</v>
       </c>
       <c r="AM29">
         <v>5.95</v>
@@ -3619,10 +4099,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G30">
         <v>824963</v>
@@ -3682,16 +4162,16 @@
         <v>0.9268</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD30">
         <v>3.67</v>
       </c>
       <c r="AE30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF30">
         <v>0.2104</v>
@@ -3711,7 +4191,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3723,31 +4203,34 @@
         <v>-155</v>
       </c>
       <c r="F31" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L31">
         <v>4</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V31" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="Z31">
+        <v>3</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3755,7 +4238,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>4.5</v>
@@ -3767,31 +4250,31 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3799,7 +4282,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33">
         <v>5.5</v>
@@ -3811,7 +4294,7 @@
         <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G33">
         <v>823180</v>
@@ -3850,7 +4333,7 @@
         <v>0.369</v>
       </c>
       <c r="S33" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="T33">
         <v>0.3543</v>
@@ -3871,16 +4354,16 @@
         <v>1.0313</v>
       </c>
       <c r="AA33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD33">
         <v>7.38</v>
       </c>
       <c r="AE33" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AF33">
         <v>0.1965</v>
